--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133344378</v>
+        <v>133344376</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635862</v>
+        <v>635914</v>
       </c>
       <c r="R2" t="n">
-        <v>6999958</v>
+        <v>6999854</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133344376</v>
+        <v>133344378</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635914</v>
+        <v>635862</v>
       </c>
       <c r="R3" t="n">
-        <v>6999854</v>
+        <v>6999958</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1130,45 +1130,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133344405</v>
+        <v>133344393</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>80474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635419</v>
+        <v>635694</v>
       </c>
       <c r="R6" t="n">
-        <v>6999913</v>
+        <v>6999911</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1200,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,8 +1222,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1237,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133344393</v>
+        <v>133344394</v>
       </c>
       <c r="B7" t="n">
-        <v>80474</v>
+        <v>80398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635694</v>
+        <v>635695</v>
       </c>
       <c r="R7" t="n">
-        <v>6999911</v>
+        <v>6999912</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1363,48 +1382,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133344394</v>
+        <v>133344405</v>
       </c>
       <c r="B8" t="n">
-        <v>80398</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635695</v>
+        <v>635419</v>
       </c>
       <c r="R8" t="n">
-        <v>6999912</v>
+        <v>6999913</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1436,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,24 +1471,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133344406</v>
+        <v>133344410</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,34 +2199,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635433</v>
+        <v>635570</v>
       </c>
       <c r="R15" t="n">
-        <v>6999899</v>
+        <v>6999790</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2258,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133344410</v>
+        <v>133344406</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,42 +2314,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635570</v>
+        <v>635433</v>
       </c>
       <c r="R16" t="n">
-        <v>6999790</v>
+        <v>6999899</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,37 +2410,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133343516</v>
+        <v>133343531</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2448,10 +2453,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636049</v>
+        <v>635688</v>
       </c>
       <c r="R17" t="n">
-        <v>6999689</v>
+        <v>6999888</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2483,7 +2488,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2498,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,24 +2507,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2536,42 +2525,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133343531</v>
+        <v>133343516</v>
       </c>
       <c r="B18" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2579,10 +2563,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635688</v>
+        <v>636049</v>
       </c>
       <c r="R18" t="n">
-        <v>6999888</v>
+        <v>6999689</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2614,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,8 +2617,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2651,32 +2651,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133344396</v>
+        <v>133344397</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635669</v>
+        <v>635665</v>
       </c>
       <c r="R19" t="n">
-        <v>6999875</v>
+        <v>6999867</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2758,7 +2758,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133344397</v>
+        <v>133343519</v>
       </c>
       <c r="B20" t="n">
         <v>91918</v>
@@ -2787,19 +2787,22 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635665</v>
+        <v>635993</v>
       </c>
       <c r="R20" t="n">
-        <v>6999867</v>
+        <v>6999755</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2828,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,69 +2850,82 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133343519</v>
+        <v>133344404</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>93206</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635993</v>
+        <v>635423</v>
       </c>
       <c r="R21" t="n">
-        <v>6999755</v>
+        <v>6999959</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2938,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,44 +2973,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344404</v>
+        <v>133344396</v>
       </c>
       <c r="B22" t="n">
-        <v>93206</v>
+        <v>91881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3002,21 +3002,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635423</v>
+        <v>635669</v>
       </c>
       <c r="R22" t="n">
-        <v>6999959</v>
+        <v>6999875</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133343549</v>
+        <v>133344413</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,45 +3569,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635842</v>
+        <v>635804</v>
       </c>
       <c r="R27" t="n">
-        <v>6999727</v>
+        <v>6999795</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3636,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3646,12 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,19 +3653,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344413</v>
+        <v>133344417</v>
       </c>
       <c r="B28" t="n">
         <v>91918</v>
@@ -3713,13 +3700,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635804</v>
+        <v>635820</v>
       </c>
       <c r="R28" t="n">
-        <v>6999795</v>
+        <v>6999730</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3748,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3758,7 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,10 +3772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133344417</v>
+        <v>133343549</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,37 +3783,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635820</v>
+        <v>635842</v>
       </c>
       <c r="R29" t="n">
-        <v>6999730</v>
+        <v>6999727</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3855,7 +3850,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3860,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133343548</v>
+        <v>133343536</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4845,34 +4845,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635839</v>
+        <v>635415</v>
       </c>
       <c r="R38" t="n">
-        <v>6999729</v>
+        <v>6999961</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4904,7 +4912,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4914,7 +4922,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4941,10 +4949,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133344407</v>
+        <v>133344389</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4952,26 +4960,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4979,10 +4992,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635393</v>
+        <v>635661</v>
       </c>
       <c r="R39" t="n">
-        <v>6999887</v>
+        <v>6999959</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -5014,7 +5027,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5024,7 +5037,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5033,24 +5046,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5067,10 +5064,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133344389</v>
+        <v>133343548</v>
       </c>
       <c r="B40" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,45 +5075,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635661</v>
+        <v>635839</v>
       </c>
       <c r="R40" t="n">
-        <v>6999959</v>
+        <v>6999729</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5145,7 +5134,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5144,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5170,22 +5159,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133343536</v>
+        <v>133344407</v>
       </c>
       <c r="B41" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,31 +5182,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5225,13 +5209,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635415</v>
+        <v>635393</v>
       </c>
       <c r="R41" t="n">
-        <v>6999961</v>
+        <v>6999887</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5260,7 +5244,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5270,7 +5254,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5279,18 +5263,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133344421</v>
+        <v>133344395</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635821</v>
+        <v>635671</v>
       </c>
       <c r="R44" t="n">
-        <v>6999726</v>
+        <v>6999877</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133344395</v>
+        <v>133344421</v>
       </c>
       <c r="B45" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635671</v>
+        <v>635821</v>
       </c>
       <c r="R45" t="n">
-        <v>6999877</v>
+        <v>6999726</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5990,37 +5990,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133343551</v>
+        <v>133344422</v>
       </c>
       <c r="B48" t="n">
-        <v>91881</v>
+        <v>57136</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6028,13 +6033,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635870</v>
+        <v>635832</v>
       </c>
       <c r="R48" t="n">
-        <v>6999720</v>
+        <v>6999733</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6063,7 +6068,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6073,7 +6078,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6082,76 +6087,55 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133344422</v>
+        <v>133343551</v>
       </c>
       <c r="B49" t="n">
-        <v>57136</v>
+        <v>91881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6159,13 +6143,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635832</v>
+        <v>635870</v>
       </c>
       <c r="R49" t="n">
-        <v>6999733</v>
+        <v>6999720</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6194,7 +6178,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6204,7 +6188,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6213,18 +6197,34 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133344376</v>
+        <v>133344378</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635914</v>
+        <v>635862</v>
       </c>
       <c r="R2" t="n">
-        <v>6999854</v>
+        <v>6999958</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,45 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133344378</v>
+        <v>133344376</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635862</v>
+        <v>635914</v>
       </c>
       <c r="R3" t="n">
-        <v>6999958</v>
+        <v>6999854</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1256,48 +1256,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133344394</v>
+        <v>133344405</v>
       </c>
       <c r="B7" t="n">
-        <v>80398</v>
+        <v>79333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635695</v>
+        <v>635419</v>
       </c>
       <c r="R7" t="n">
-        <v>6999912</v>
+        <v>6999913</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1329,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,24 +1345,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,45 +1363,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133344405</v>
+        <v>133344394</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635419</v>
+        <v>635695</v>
       </c>
       <c r="R8" t="n">
-        <v>6999913</v>
+        <v>6999912</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1452,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,8 +1455,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133344410</v>
+        <v>133344406</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,42 +2199,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635570</v>
+        <v>635433</v>
       </c>
       <c r="R15" t="n">
-        <v>6999790</v>
+        <v>6999899</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2266,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133344406</v>
+        <v>133343516</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,37 +2306,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635433</v>
+        <v>636049</v>
       </c>
       <c r="R16" t="n">
-        <v>6999899</v>
+        <v>6999689</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2373,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,50 +2387,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133343531</v>
+        <v>133344410</v>
       </c>
       <c r="B17" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,7 +2454,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2453,13 +2464,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635688</v>
+        <v>635570</v>
       </c>
       <c r="R17" t="n">
-        <v>6999888</v>
+        <v>6999790</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2488,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2498,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,49 +2524,54 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133343516</v>
+        <v>133343531</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2563,10 +2579,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636049</v>
+        <v>635688</v>
       </c>
       <c r="R18" t="n">
-        <v>6999689</v>
+        <v>6999888</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2598,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,24 +2633,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2651,10 +2651,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133344397</v>
+        <v>133344391</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2662,34 +2662,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635665</v>
+        <v>635694</v>
       </c>
       <c r="R19" t="n">
-        <v>6999867</v>
+        <v>6999907</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2721,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,8 +2743,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2758,51 +2777,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133343519</v>
+        <v>133344404</v>
       </c>
       <c r="B20" t="n">
-        <v>91918</v>
+        <v>93206</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635993</v>
+        <v>635423</v>
       </c>
       <c r="R20" t="n">
-        <v>6999755</v>
+        <v>6999959</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2831,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,44 +2866,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133344404</v>
+        <v>133344396</v>
       </c>
       <c r="B21" t="n">
-        <v>93206</v>
+        <v>91881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635423</v>
+        <v>635669</v>
       </c>
       <c r="R21" t="n">
-        <v>6999959</v>
+        <v>6999875</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,32 +2991,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344396</v>
+        <v>133344397</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635669</v>
+        <v>635665</v>
       </c>
       <c r="R22" t="n">
-        <v>6999875</v>
+        <v>6999867</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133344391</v>
+        <v>133343519</v>
       </c>
       <c r="B23" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635694</v>
+        <v>635993</v>
       </c>
       <c r="R23" t="n">
-        <v>6999907</v>
+        <v>6999755</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,73 +3196,85 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133344374</v>
+        <v>133344388</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635973</v>
+        <v>635662</v>
       </c>
       <c r="R24" t="n">
-        <v>6999760</v>
+        <v>6999959</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3294,7 +3306,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3304,7 +3316,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3313,6 +3325,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3331,10 +3344,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344375</v>
+        <v>133344374</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3342,21 +3355,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3366,10 +3379,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635987</v>
+        <v>635973</v>
       </c>
       <c r="R25" t="n">
-        <v>6999806</v>
+        <v>6999760</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3401,7 +3414,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3411,7 +3424,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,57 +3451,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133344388</v>
+        <v>133344375</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635662</v>
+        <v>635987</v>
       </c>
       <c r="R26" t="n">
-        <v>6999959</v>
+        <v>6999806</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3520,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,7 +3540,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133344413</v>
+        <v>133343549</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,37 +3569,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635804</v>
+        <v>635842</v>
       </c>
       <c r="R27" t="n">
-        <v>6999795</v>
+        <v>6999727</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3636,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3646,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,19 +3666,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344417</v>
+        <v>133344413</v>
       </c>
       <c r="B28" t="n">
         <v>91918</v>
@@ -3700,13 +3713,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635820</v>
+        <v>635804</v>
       </c>
       <c r="R28" t="n">
-        <v>6999730</v>
+        <v>6999795</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,7 +3748,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3758,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,10 +3785,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133343549</v>
+        <v>133344417</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,45 +3796,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635842</v>
+        <v>635820</v>
       </c>
       <c r="R29" t="n">
-        <v>6999727</v>
+        <v>6999730</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3850,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3860,12 +3865,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,22 +3880,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133344416</v>
+        <v>133344398</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,37 +3903,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635824</v>
+        <v>635670</v>
       </c>
       <c r="R30" t="n">
-        <v>6999739</v>
+        <v>6999849</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -3965,7 +3962,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3972,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,24 +3981,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4018,10 +3999,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344398</v>
+        <v>133344416</v>
       </c>
       <c r="B31" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4029,34 +4010,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635670</v>
+        <v>635824</v>
       </c>
       <c r="R31" t="n">
-        <v>6999849</v>
+        <v>6999739</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4088,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4098,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4107,8 +4091,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R35" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B36" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R36" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133343536</v>
+        <v>133343548</v>
       </c>
       <c r="B38" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4845,42 +4845,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635415</v>
+        <v>635839</v>
       </c>
       <c r="R38" t="n">
-        <v>6999961</v>
+        <v>6999729</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4912,7 +4904,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4922,7 +4914,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4949,10 +4941,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133344389</v>
+        <v>133344407</v>
       </c>
       <c r="B39" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,31 +4952,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4992,10 +4979,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635661</v>
+        <v>635393</v>
       </c>
       <c r="R39" t="n">
-        <v>6999959</v>
+        <v>6999887</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -5027,7 +5014,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5037,7 +5024,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5046,8 +5033,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5064,10 +5067,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133343548</v>
+        <v>133343536</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5075,34 +5078,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635839</v>
+        <v>635415</v>
       </c>
       <c r="R40" t="n">
-        <v>6999729</v>
+        <v>6999961</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5134,7 +5145,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5144,7 +5155,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5171,10 +5182,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133344407</v>
+        <v>133344389</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5182,26 +5193,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5209,10 +5225,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635393</v>
+        <v>635661</v>
       </c>
       <c r="R41" t="n">
-        <v>6999887</v>
+        <v>6999959</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -5244,7 +5260,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5254,7 +5270,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5263,24 +5279,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5990,42 +5990,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133344422</v>
+        <v>133343551</v>
       </c>
       <c r="B48" t="n">
-        <v>57136</v>
+        <v>91881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6033,13 +6028,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635832</v>
+        <v>635870</v>
       </c>
       <c r="R48" t="n">
-        <v>6999733</v>
+        <v>6999720</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6068,7 +6063,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6078,7 +6073,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6087,55 +6082,76 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133343551</v>
+        <v>133344422</v>
       </c>
       <c r="B49" t="n">
-        <v>91881</v>
+        <v>57136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6143,13 +6159,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635870</v>
+        <v>635832</v>
       </c>
       <c r="R49" t="n">
-        <v>6999720</v>
+        <v>6999733</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6178,7 +6194,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6188,7 +6204,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6197,34 +6213,18 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6352,6 +6352,715 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>133566388</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Tjuvtoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>635934</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6999625</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>133566389</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tjuvtoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>635931</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6999628</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>133566448</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80466</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tjuvtoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>635576</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7000018</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133566383</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tjuvtoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>635973</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6999599</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>133573160</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tjuvtoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>635279</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6999958</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133573131</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Tjuvdoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>635838</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6999713</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -2188,48 +2188,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133344406</v>
+        <v>133343531</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635433</v>
+        <v>635688</v>
       </c>
       <c r="R15" t="n">
-        <v>6999899</v>
+        <v>6999888</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2258,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,22 +2291,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133343516</v>
+        <v>133344406</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,40 +2314,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636049</v>
+        <v>635433</v>
       </c>
       <c r="R16" t="n">
-        <v>6999689</v>
+        <v>6999899</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2368,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,44 +2392,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133344410</v>
+        <v>133343516</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,31 +2421,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2464,13 +2448,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635570</v>
+        <v>636049</v>
       </c>
       <c r="R17" t="n">
-        <v>6999790</v>
+        <v>6999689</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,7 +2483,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2493,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,50 +2502,66 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133343531</v>
+        <v>133344410</v>
       </c>
       <c r="B18" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2569,7 +2569,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2579,13 +2579,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635688</v>
+        <v>635570</v>
       </c>
       <c r="R18" t="n">
-        <v>6999888</v>
+        <v>6999790</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,12 +2639,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2777,32 +2777,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133344404</v>
+        <v>133344397</v>
       </c>
       <c r="B20" t="n">
-        <v>93206</v>
+        <v>91918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635423</v>
+        <v>635665</v>
       </c>
       <c r="R20" t="n">
-        <v>6999959</v>
+        <v>6999867</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,48 +2884,51 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133344396</v>
+        <v>133343519</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635669</v>
+        <v>635993</v>
       </c>
       <c r="R21" t="n">
-        <v>6999875</v>
+        <v>6999755</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2954,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2967,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,50 +2976,66 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344397</v>
+        <v>133344404</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>93206</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3026,10 +3045,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635665</v>
+        <v>635423</v>
       </c>
       <c r="R22" t="n">
-        <v>6999867</v>
+        <v>6999959</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3061,7 +3080,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3090,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,51 +3117,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133343519</v>
+        <v>133344396</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635993</v>
+        <v>635669</v>
       </c>
       <c r="R23" t="n">
-        <v>6999755</v>
+        <v>6999875</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3171,7 +3187,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3197,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,91 +3206,63 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133344388</v>
+        <v>133344374</v>
       </c>
       <c r="B24" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635662</v>
+        <v>635973</v>
       </c>
       <c r="R24" t="n">
-        <v>6999959</v>
+        <v>6999760</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3306,7 +3294,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3316,7 +3304,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3325,7 +3313,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3344,10 +3331,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344374</v>
+        <v>133344375</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,21 +3342,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3379,10 +3366,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635973</v>
+        <v>635987</v>
       </c>
       <c r="R25" t="n">
-        <v>6999760</v>
+        <v>6999806</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3414,7 +3401,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3424,7 +3411,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3451,45 +3438,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133344375</v>
+        <v>133344388</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635987</v>
+        <v>635662</v>
       </c>
       <c r="R26" t="n">
-        <v>6999806</v>
+        <v>6999959</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3521,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3530,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,6 +3539,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133343549</v>
+        <v>133344413</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,45 +3569,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635842</v>
+        <v>635804</v>
       </c>
       <c r="R27" t="n">
-        <v>6999727</v>
+        <v>6999795</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3636,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3646,12 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,19 +3653,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344413</v>
+        <v>133344417</v>
       </c>
       <c r="B28" t="n">
         <v>91918</v>
@@ -3713,13 +3700,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635804</v>
+        <v>635820</v>
       </c>
       <c r="R28" t="n">
-        <v>6999795</v>
+        <v>6999730</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3748,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3758,7 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,10 +3772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133344417</v>
+        <v>133343549</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,37 +3783,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635820</v>
+        <v>635842</v>
       </c>
       <c r="R29" t="n">
-        <v>6999730</v>
+        <v>6999727</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3855,7 +3850,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3860,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,22 +3880,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133344398</v>
+        <v>133344416</v>
       </c>
       <c r="B30" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,34 +3903,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635670</v>
+        <v>635824</v>
       </c>
       <c r="R30" t="n">
-        <v>6999849</v>
+        <v>6999739</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -3962,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3972,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3981,8 +3984,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3999,10 +4018,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344416</v>
+        <v>133344398</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4010,37 +4029,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635824</v>
+        <v>635670</v>
       </c>
       <c r="R31" t="n">
-        <v>6999739</v>
+        <v>6999849</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4072,7 +4088,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4098,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4091,24 +4107,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4245,10 +4245,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133344402</v>
+        <v>133343517</v>
       </c>
       <c r="B33" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635439</v>
+        <v>636054</v>
       </c>
       <c r="R33" t="n">
-        <v>6999963</v>
+        <v>6999703</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,38 +4343,38 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133343517</v>
+        <v>133344402</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4409,13 +4409,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636054</v>
+        <v>635439</v>
       </c>
       <c r="R34" t="n">
-        <v>6999703</v>
+        <v>6999963</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4469,38 +4469,38 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B35" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R35" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B36" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R36" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133343547</v>
+        <v>133344377</v>
       </c>
       <c r="B47" t="n">
-        <v>91918</v>
+        <v>58119</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5875,40 +5875,53 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635812</v>
+        <v>635919</v>
       </c>
       <c r="R47" t="n">
-        <v>6999735</v>
+        <v>6999871</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5937,7 +5950,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5947,7 +5960,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5956,66 +5969,50 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133343551</v>
+        <v>133343547</v>
       </c>
       <c r="B48" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6028,10 +6025,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635870</v>
+        <v>635812</v>
       </c>
       <c r="R48" t="n">
-        <v>6999720</v>
+        <v>6999735</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6063,7 +6060,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6073,7 +6070,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6116,42 +6113,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133344422</v>
+        <v>133343551</v>
       </c>
       <c r="B49" t="n">
-        <v>57136</v>
+        <v>91881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6159,13 +6151,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635832</v>
+        <v>635870</v>
       </c>
       <c r="R49" t="n">
-        <v>6999733</v>
+        <v>6999720</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6194,7 +6186,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6204,7 +6196,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6213,28 +6205,44 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133344377</v>
+        <v>133344422</v>
       </c>
       <c r="B50" t="n">
-        <v>58119</v>
+        <v>57136</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6242,50 +6250,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635919</v>
+        <v>635832</v>
       </c>
       <c r="R50" t="n">
-        <v>6999871</v>
+        <v>6999733</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6354,53 +6354,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566388</v>
+        <v>133566448</v>
       </c>
       <c r="B51" t="n">
-        <v>57955</v>
+        <v>80466</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635934</v>
+        <v>635576</v>
       </c>
       <c r="R51" t="n">
-        <v>6999625</v>
+        <v>7000018</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6432,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6442,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6469,7 +6461,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566389</v>
+        <v>133566388</v>
       </c>
       <c r="B52" t="n">
         <v>57955</v>
@@ -6512,10 +6504,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635931</v>
+        <v>635934</v>
       </c>
       <c r="R52" t="n">
-        <v>6999628</v>
+        <v>6999625</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6547,7 +6539,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6557,7 +6549,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6584,45 +6576,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133566448</v>
+        <v>133566389</v>
       </c>
       <c r="B53" t="n">
-        <v>80466</v>
+        <v>57955</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635576</v>
+        <v>635931</v>
       </c>
       <c r="R53" t="n">
-        <v>7000018</v>
+        <v>6999628</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6817,60 +6817,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R55" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6899,7 +6890,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6909,7 +6900,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6921,6 +6912,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6937,51 +6943,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B56" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R56" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7010,7 +7025,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7020,7 +7035,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7032,21 +7047,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133344378</v>
+        <v>133344376</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635862</v>
+        <v>635914</v>
       </c>
       <c r="R2" t="n">
-        <v>6999958</v>
+        <v>6999854</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133344376</v>
+        <v>133344378</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635914</v>
+        <v>635862</v>
       </c>
       <c r="R3" t="n">
-        <v>6999854</v>
+        <v>6999958</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133344393</v>
+        <v>133344394</v>
       </c>
       <c r="B6" t="n">
-        <v>80474</v>
+        <v>80398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635694</v>
+        <v>635695</v>
       </c>
       <c r="R6" t="n">
-        <v>6999911</v>
+        <v>6999912</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1256,45 +1256,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133344405</v>
+        <v>133344393</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>80474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635419</v>
+        <v>635694</v>
       </c>
       <c r="R7" t="n">
-        <v>6999913</v>
+        <v>6999911</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1326,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,8 +1348,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1363,48 +1382,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133344394</v>
+        <v>133344405</v>
       </c>
       <c r="B8" t="n">
-        <v>80398</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635695</v>
+        <v>635419</v>
       </c>
       <c r="R8" t="n">
-        <v>6999912</v>
+        <v>6999913</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1436,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,24 +1471,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133344419</v>
+        <v>133344399</v>
       </c>
       <c r="B13" t="n">
         <v>91881</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635818</v>
+        <v>635669</v>
       </c>
       <c r="R13" t="n">
-        <v>6999728</v>
+        <v>6999846</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133344399</v>
+        <v>133344419</v>
       </c>
       <c r="B14" t="n">
         <v>91881</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635669</v>
+        <v>635818</v>
       </c>
       <c r="R14" t="n">
-        <v>6999846</v>
+        <v>6999728</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,42 +2188,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133343531</v>
+        <v>133343516</v>
       </c>
       <c r="B15" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2231,10 +2226,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635688</v>
+        <v>636049</v>
       </c>
       <c r="R15" t="n">
-        <v>6999888</v>
+        <v>6999689</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2266,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,8 +2280,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2410,10 +2421,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133343516</v>
+        <v>133344410</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,26 +2432,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2448,13 +2464,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636049</v>
+        <v>635570</v>
       </c>
       <c r="R17" t="n">
-        <v>6999689</v>
+        <v>6999790</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2483,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,66 +2518,50 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133344410</v>
+        <v>133343531</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2569,7 +2569,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2579,13 +2579,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635570</v>
+        <v>635688</v>
       </c>
       <c r="R18" t="n">
-        <v>6999790</v>
+        <v>6999888</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,60 +2639,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133344391</v>
+        <v>133344396</v>
       </c>
       <c r="B19" t="n">
-        <v>80438</v>
+        <v>91881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635694</v>
+        <v>635669</v>
       </c>
       <c r="R19" t="n">
-        <v>6999907</v>
+        <v>6999875</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2724,7 +2721,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2731,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,24 +2740,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2777,32 +2758,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133344397</v>
+        <v>133344404</v>
       </c>
       <c r="B20" t="n">
-        <v>91918</v>
+        <v>93206</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2812,10 +2793,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635665</v>
+        <v>635423</v>
       </c>
       <c r="R20" t="n">
-        <v>6999867</v>
+        <v>6999959</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2847,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2857,7 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133343519</v>
+        <v>133344391</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2922,13 +2903,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635993</v>
+        <v>635694</v>
       </c>
       <c r="R21" t="n">
-        <v>6999755</v>
+        <v>6999907</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2957,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,60 +2963,60 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344404</v>
+        <v>133344397</v>
       </c>
       <c r="B22" t="n">
-        <v>93206</v>
+        <v>91918</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3045,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635423</v>
+        <v>635665</v>
       </c>
       <c r="R22" t="n">
-        <v>6999959</v>
+        <v>6999867</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3080,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3090,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,48 +3098,51 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133344396</v>
+        <v>133343519</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635669</v>
+        <v>635993</v>
       </c>
       <c r="R23" t="n">
-        <v>6999875</v>
+        <v>6999755</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3187,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3197,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,28 +3190,44 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133344374</v>
+        <v>133344375</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,21 +3235,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635973</v>
+        <v>635987</v>
       </c>
       <c r="R24" t="n">
-        <v>6999760</v>
+        <v>6999806</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3331,10 +3331,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344375</v>
+        <v>133344374</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3342,21 +3342,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635987</v>
+        <v>635973</v>
       </c>
       <c r="R25" t="n">
-        <v>6999806</v>
+        <v>6999760</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4245,10 +4245,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133343517</v>
+        <v>133344402</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636054</v>
+        <v>635439</v>
       </c>
       <c r="R33" t="n">
-        <v>6999703</v>
+        <v>6999963</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,38 +4343,38 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133344402</v>
+        <v>133343517</v>
       </c>
       <c r="B34" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4409,13 +4409,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635439</v>
+        <v>636054</v>
       </c>
       <c r="R34" t="n">
-        <v>6999963</v>
+        <v>6999703</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4469,38 +4469,38 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R35" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B36" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R36" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133343548</v>
+        <v>133344389</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4845,37 +4845,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635839</v>
+        <v>635661</v>
       </c>
       <c r="R38" t="n">
-        <v>6999729</v>
+        <v>6999959</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4904,7 +4912,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4914,7 +4922,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4929,12 +4937,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5067,10 +5075,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133343536</v>
+        <v>133343548</v>
       </c>
       <c r="B40" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,42 +5086,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635415</v>
+        <v>635839</v>
       </c>
       <c r="R40" t="n">
-        <v>6999961</v>
+        <v>6999729</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5182,10 +5182,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133344389</v>
+        <v>133343536</v>
       </c>
       <c r="B41" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,16 +5193,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5215,7 +5215,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635661</v>
+        <v>635415</v>
       </c>
       <c r="R41" t="n">
-        <v>6999959</v>
+        <v>6999961</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5285,12 +5285,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133344395</v>
+        <v>133344421</v>
       </c>
       <c r="B44" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635671</v>
+        <v>635821</v>
       </c>
       <c r="R44" t="n">
-        <v>6999877</v>
+        <v>6999726</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133344421</v>
+        <v>133344395</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635821</v>
+        <v>635671</v>
       </c>
       <c r="R45" t="n">
-        <v>6999726</v>
+        <v>6999877</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5864,10 +5864,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133344377</v>
+        <v>133344422</v>
       </c>
       <c r="B47" t="n">
-        <v>58119</v>
+        <v>57136</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5875,50 +5875,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635919</v>
+        <v>635832</v>
       </c>
       <c r="R47" t="n">
-        <v>6999871</v>
+        <v>6999733</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5950,7 +5942,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5960,7 +5952,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5987,10 +5979,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133343547</v>
+        <v>133344377</v>
       </c>
       <c r="B48" t="n">
-        <v>91918</v>
+        <v>58119</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5998,40 +5990,53 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635812</v>
+        <v>635919</v>
       </c>
       <c r="R48" t="n">
-        <v>6999735</v>
+        <v>6999871</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6060,7 +6065,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6070,7 +6075,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6079,34 +6084,18 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6239,10 +6228,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133344422</v>
+        <v>133343547</v>
       </c>
       <c r="B50" t="n">
-        <v>57136</v>
+        <v>91918</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,31 +6239,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6282,13 +6266,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635832</v>
+        <v>635812</v>
       </c>
       <c r="R50" t="n">
-        <v>6999733</v>
+        <v>6999735</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6317,7 +6301,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6327,7 +6311,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6336,18 +6320,34 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6817,51 +6817,60 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B55" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R55" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6890,7 +6899,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6900,7 +6909,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6912,21 +6921,6 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6943,60 +6937,51 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B56" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R56" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7025,7 +7010,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7035,7 +7020,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7047,6 +7032,21 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -3331,45 +3331,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344374</v>
+        <v>133344388</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635973</v>
+        <v>635662</v>
       </c>
       <c r="R25" t="n">
-        <v>6999760</v>
+        <v>6999959</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3401,7 +3413,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3411,7 +3423,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,6 +3432,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3438,57 +3451,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133344388</v>
+        <v>133344374</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635662</v>
+        <v>635973</v>
       </c>
       <c r="R26" t="n">
-        <v>6999959</v>
+        <v>6999760</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3520,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,7 +3540,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B35" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R35" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B36" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R36" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5297,48 +5297,60 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B42" t="n">
-        <v>92217</v>
+        <v>99130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R42" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5367,7 +5379,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5386,78 +5398,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R43" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5496,7 +5497,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,19 +5506,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6817,60 +6817,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R55" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6899,7 +6890,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6909,7 +6900,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6921,6 +6912,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6937,51 +6943,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B56" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R56" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7010,7 +7025,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7020,7 +7035,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7032,21 +7047,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133344376</v>
+        <v>133344378</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635914</v>
+        <v>635862</v>
       </c>
       <c r="R2" t="n">
-        <v>6999854</v>
+        <v>6999958</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,45 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133344378</v>
+        <v>133344376</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635862</v>
+        <v>635914</v>
       </c>
       <c r="R3" t="n">
-        <v>6999958</v>
+        <v>6999854</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133344394</v>
+        <v>133344393</v>
       </c>
       <c r="B6" t="n">
-        <v>80398</v>
+        <v>80474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635695</v>
+        <v>635694</v>
       </c>
       <c r="R6" t="n">
-        <v>6999912</v>
+        <v>6999911</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1256,48 +1256,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133344393</v>
+        <v>133344405</v>
       </c>
       <c r="B7" t="n">
-        <v>80474</v>
+        <v>79333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635694</v>
+        <v>635419</v>
       </c>
       <c r="R7" t="n">
-        <v>6999911</v>
+        <v>6999913</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1329,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,24 +1345,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,45 +1363,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133344405</v>
+        <v>133344394</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635419</v>
+        <v>635695</v>
       </c>
       <c r="R8" t="n">
-        <v>6999913</v>
+        <v>6999912</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1452,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,8 +1455,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133344399</v>
+        <v>133344419</v>
       </c>
       <c r="B13" t="n">
         <v>91881</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635669</v>
+        <v>635818</v>
       </c>
       <c r="R13" t="n">
-        <v>6999846</v>
+        <v>6999728</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133344419</v>
+        <v>133344399</v>
       </c>
       <c r="B14" t="n">
         <v>91881</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635818</v>
+        <v>635669</v>
       </c>
       <c r="R14" t="n">
-        <v>6999728</v>
+        <v>6999846</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133343516</v>
+        <v>133344406</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,40 +2199,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636049</v>
+        <v>635433</v>
       </c>
       <c r="R15" t="n">
-        <v>6999689</v>
+        <v>6999899</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2261,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,44 +2277,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133344406</v>
+        <v>133343516</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,37 +2306,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635433</v>
+        <v>636049</v>
       </c>
       <c r="R16" t="n">
-        <v>6999899</v>
+        <v>6999689</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2384,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2394,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,18 +2387,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2651,48 +2651,51 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133344396</v>
+        <v>133343519</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635669</v>
+        <v>635993</v>
       </c>
       <c r="R19" t="n">
-        <v>6999875</v>
+        <v>6999755</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2721,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,50 +2743,66 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133344404</v>
+        <v>133344397</v>
       </c>
       <c r="B20" t="n">
-        <v>93206</v>
+        <v>91918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2793,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635423</v>
+        <v>635665</v>
       </c>
       <c r="R20" t="n">
-        <v>6999959</v>
+        <v>6999867</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2828,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,48 +2884,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133344391</v>
+        <v>133344404</v>
       </c>
       <c r="B21" t="n">
-        <v>80438</v>
+        <v>93206</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635694</v>
+        <v>635423</v>
       </c>
       <c r="R21" t="n">
-        <v>6999907</v>
+        <v>6999959</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2938,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,24 +2973,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2991,32 +2991,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344397</v>
+        <v>133344396</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635665</v>
+        <v>635669</v>
       </c>
       <c r="R22" t="n">
-        <v>6999867</v>
+        <v>6999875</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133343519</v>
+        <v>133344391</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635993</v>
+        <v>635694</v>
       </c>
       <c r="R23" t="n">
-        <v>6999755</v>
+        <v>6999907</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,38 +3196,38 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133344375</v>
+        <v>133344374</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,21 +3235,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635987</v>
+        <v>635973</v>
       </c>
       <c r="R24" t="n">
-        <v>6999806</v>
+        <v>6999760</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3451,10 +3451,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133344374</v>
+        <v>133344375</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635973</v>
+        <v>635987</v>
       </c>
       <c r="R26" t="n">
-        <v>6999760</v>
+        <v>6999806</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3558,7 +3558,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133344413</v>
+        <v>133344417</v>
       </c>
       <c r="B27" t="n">
         <v>91918</v>
@@ -3593,13 +3593,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635804</v>
+        <v>635820</v>
       </c>
       <c r="R27" t="n">
-        <v>6999795</v>
+        <v>6999730</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,7 +3665,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344417</v>
+        <v>133344413</v>
       </c>
       <c r="B28" t="n">
         <v>91918</v>
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635820</v>
+        <v>635804</v>
       </c>
       <c r="R28" t="n">
-        <v>6999730</v>
+        <v>6999795</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3892,10 +3892,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133344416</v>
+        <v>133344398</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,37 +3903,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635824</v>
+        <v>635670</v>
       </c>
       <c r="R30" t="n">
-        <v>6999739</v>
+        <v>6999849</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -3965,7 +3962,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3972,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,24 +3981,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4018,48 +3999,60 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344398</v>
+        <v>133344390</v>
       </c>
       <c r="B31" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635670</v>
+        <v>635693</v>
       </c>
       <c r="R31" t="n">
-        <v>6999849</v>
+        <v>6999909</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4088,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4098,7 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4107,6 +4100,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4125,46 +4119,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4172,13 +4157,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R32" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4207,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4202,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4229,6 +4214,21 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4834,10 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133344389</v>
+        <v>133343548</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4845,45 +4845,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635661</v>
+        <v>635839</v>
       </c>
       <c r="R38" t="n">
-        <v>6999959</v>
+        <v>6999729</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4912,7 +4904,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4922,7 +4914,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4937,12 +4929,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5075,10 +5067,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133343548</v>
+        <v>133344389</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,37 +5078,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635839</v>
+        <v>635661</v>
       </c>
       <c r="R40" t="n">
-        <v>6999729</v>
+        <v>6999959</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5170,12 +5170,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5297,60 +5297,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R42" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5379,7 +5367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5389,7 +5377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5398,67 +5386,78 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B43" t="n">
-        <v>92217</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R43" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5487,7 +5486,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,7 +5496,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5506,28 +5505,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133344421</v>
+        <v>133344395</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635821</v>
+        <v>635671</v>
       </c>
       <c r="R44" t="n">
-        <v>6999726</v>
+        <v>6999877</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133344395</v>
+        <v>133344421</v>
       </c>
       <c r="B45" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635671</v>
+        <v>635821</v>
       </c>
       <c r="R45" t="n">
-        <v>6999877</v>
+        <v>6999726</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5864,10 +5864,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133344422</v>
+        <v>133343547</v>
       </c>
       <c r="B47" t="n">
-        <v>57136</v>
+        <v>91918</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5875,31 +5875,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5907,13 +5902,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635832</v>
+        <v>635812</v>
       </c>
       <c r="R47" t="n">
-        <v>6999733</v>
+        <v>6999735</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5942,7 +5937,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5952,7 +5947,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5961,82 +5956,85 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133344377</v>
+        <v>133343551</v>
       </c>
       <c r="B48" t="n">
-        <v>58119</v>
+        <v>91881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635919</v>
+        <v>635870</v>
       </c>
       <c r="R48" t="n">
-        <v>6999871</v>
+        <v>6999720</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6065,7 +6063,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6075,7 +6073,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6084,55 +6082,76 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133343551</v>
+        <v>133344422</v>
       </c>
       <c r="B49" t="n">
-        <v>91881</v>
+        <v>57136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6140,13 +6159,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635870</v>
+        <v>635832</v>
       </c>
       <c r="R49" t="n">
-        <v>6999720</v>
+        <v>6999733</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6175,7 +6194,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6185,7 +6204,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6194,44 +6213,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133343547</v>
+        <v>133344377</v>
       </c>
       <c r="B50" t="n">
-        <v>91918</v>
+        <v>58119</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6239,40 +6242,53 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635812</v>
+        <v>635919</v>
       </c>
       <c r="R50" t="n">
-        <v>6999735</v>
+        <v>6999871</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6301,7 +6317,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6311,7 +6327,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6320,79 +6336,71 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566448</v>
+        <v>133566388</v>
       </c>
       <c r="B51" t="n">
-        <v>80466</v>
+        <v>57955</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635576</v>
+        <v>635934</v>
       </c>
       <c r="R51" t="n">
-        <v>7000018</v>
+        <v>6999625</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6424,7 +6432,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6442,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6461,7 +6469,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566388</v>
+        <v>133566389</v>
       </c>
       <c r="B52" t="n">
         <v>57955</v>
@@ -6504,10 +6512,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635934</v>
+        <v>635931</v>
       </c>
       <c r="R52" t="n">
-        <v>6999625</v>
+        <v>6999628</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6539,7 +6547,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6549,7 +6557,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6576,53 +6584,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133566389</v>
+        <v>133566448</v>
       </c>
       <c r="B53" t="n">
-        <v>57955</v>
+        <v>80466</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635931</v>
+        <v>635576</v>
       </c>
       <c r="R53" t="n">
-        <v>6999628</v>
+        <v>7000018</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6817,51 +6817,60 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B55" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R55" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6890,7 +6899,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6900,7 +6909,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6912,21 +6921,6 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6943,60 +6937,51 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B56" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R56" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7025,7 +7010,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7035,7 +7020,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7047,6 +7032,21 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133344393</v>
+        <v>133344394</v>
       </c>
       <c r="B6" t="n">
-        <v>80474</v>
+        <v>80398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635694</v>
+        <v>635695</v>
       </c>
       <c r="R6" t="n">
-        <v>6999911</v>
+        <v>6999912</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1256,45 +1256,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133344405</v>
+        <v>133344393</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>80474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635419</v>
+        <v>635694</v>
       </c>
       <c r="R7" t="n">
-        <v>6999913</v>
+        <v>6999911</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1326,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,8 +1348,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1363,48 +1382,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133344394</v>
+        <v>133344405</v>
       </c>
       <c r="B8" t="n">
-        <v>80398</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635695</v>
+        <v>635419</v>
       </c>
       <c r="R8" t="n">
-        <v>6999912</v>
+        <v>6999913</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1436,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,24 +1471,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -4834,10 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133343548</v>
+        <v>133343536</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4845,34 +4845,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635839</v>
+        <v>635415</v>
       </c>
       <c r="R38" t="n">
-        <v>6999729</v>
+        <v>6999961</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4904,7 +4912,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4914,7 +4922,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4941,7 +4949,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133344407</v>
+        <v>133343548</v>
       </c>
       <c r="B39" t="n">
         <v>79333</v>
@@ -4970,22 +4978,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635393</v>
+        <v>635839</v>
       </c>
       <c r="R39" t="n">
-        <v>6999887</v>
+        <v>6999729</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5014,7 +5019,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5024,7 +5029,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5033,44 +5038,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133344389</v>
+        <v>133344407</v>
       </c>
       <c r="B40" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,31 +5067,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5110,10 +5094,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635661</v>
+        <v>635393</v>
       </c>
       <c r="R40" t="n">
-        <v>6999959</v>
+        <v>6999887</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5145,7 +5129,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5139,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5164,8 +5148,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5182,10 +5182,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133343536</v>
+        <v>133344389</v>
       </c>
       <c r="B41" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,16 +5193,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5215,7 +5215,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635415</v>
+        <v>635661</v>
       </c>
       <c r="R41" t="n">
-        <v>6999961</v>
+        <v>6999959</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5285,60 +5285,72 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B42" t="n">
-        <v>92217</v>
+        <v>99130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R42" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5367,7 +5379,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5386,78 +5398,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R43" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5496,7 +5497,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,19 +5506,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6354,53 +6354,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566388</v>
+        <v>133566448</v>
       </c>
       <c r="B51" t="n">
-        <v>57955</v>
+        <v>80466</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635934</v>
+        <v>635576</v>
       </c>
       <c r="R51" t="n">
-        <v>6999625</v>
+        <v>7000018</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6432,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6442,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6469,7 +6461,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566389</v>
+        <v>133566388</v>
       </c>
       <c r="B52" t="n">
         <v>57955</v>
@@ -6512,10 +6504,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635931</v>
+        <v>635934</v>
       </c>
       <c r="R52" t="n">
-        <v>6999628</v>
+        <v>6999625</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6547,7 +6539,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6557,7 +6549,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6584,45 +6576,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133566448</v>
+        <v>133566389</v>
       </c>
       <c r="B53" t="n">
-        <v>80466</v>
+        <v>57955</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635576</v>
+        <v>635931</v>
       </c>
       <c r="R53" t="n">
-        <v>7000018</v>
+        <v>6999628</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -3331,57 +3331,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344388</v>
+        <v>133344375</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635662</v>
+        <v>635987</v>
       </c>
       <c r="R25" t="n">
-        <v>6999959</v>
+        <v>6999806</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3413,7 +3401,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3423,7 +3411,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,7 +3420,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3451,45 +3438,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133344375</v>
+        <v>133344388</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635987</v>
+        <v>635662</v>
       </c>
       <c r="R26" t="n">
-        <v>6999806</v>
+        <v>6999959</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3521,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3530,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,6 +3539,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -5297,60 +5297,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R42" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5379,7 +5367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5389,7 +5377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5398,67 +5386,78 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B43" t="n">
-        <v>92217</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R43" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5487,7 +5486,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,7 +5496,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5506,18 +5505,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -3331,45 +3331,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344375</v>
+        <v>133344388</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635987</v>
+        <v>635662</v>
       </c>
       <c r="R25" t="n">
-        <v>6999806</v>
+        <v>6999959</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3401,7 +3413,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3411,7 +3423,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,6 +3432,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3438,57 +3451,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133344388</v>
+        <v>133344375</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635662</v>
+        <v>635987</v>
       </c>
       <c r="R26" t="n">
-        <v>6999959</v>
+        <v>6999806</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3520,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,7 +3540,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3999,46 +3999,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4046,13 +4037,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R31" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4081,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4091,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4103,6 +4094,21 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4119,37 +4125,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4157,13 +4172,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R32" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4192,7 +4207,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4202,7 +4217,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4214,21 +4229,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -3331,57 +3331,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344388</v>
+        <v>133344375</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635662</v>
+        <v>635987</v>
       </c>
       <c r="R25" t="n">
-        <v>6999959</v>
+        <v>6999806</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3413,7 +3401,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3423,7 +3411,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,7 +3420,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3451,45 +3438,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133344375</v>
+        <v>133344388</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635987</v>
+        <v>635662</v>
       </c>
       <c r="R26" t="n">
-        <v>6999806</v>
+        <v>6999959</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3521,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3530,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,6 +3539,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3999,37 +3999,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4037,13 +4046,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R31" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4072,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4094,21 +4103,6 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4125,46 +4119,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4172,13 +4157,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R32" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4207,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4202,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4229,6 +4214,21 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -5297,48 +5297,60 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B42" t="n">
-        <v>92217</v>
+        <v>99130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R42" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5367,7 +5379,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5386,78 +5398,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R43" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5496,7 +5497,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,19 +5506,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133344378</v>
+        <v>133344376</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635862</v>
+        <v>635914</v>
       </c>
       <c r="R2" t="n">
-        <v>6999958</v>
+        <v>6999854</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133344376</v>
+        <v>133344378</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>91883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635914</v>
+        <v>635862</v>
       </c>
       <c r="R3" t="n">
-        <v>6999854</v>
+        <v>6999958</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +900,7 @@
         <v>133344392</v>
       </c>
       <c r="B4" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>133344424</v>
       </c>
       <c r="B5" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>133344394</v>
       </c>
       <c r="B6" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>133344393</v>
       </c>
       <c r="B7" t="n">
-        <v>80474</v>
+        <v>80475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>133344405</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>133343521</v>
       </c>
       <c r="B9" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>133343546</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>133343520</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>133343545</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>133344419</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>133344399</v>
       </c>
       <c r="B14" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>133344406</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>133343516</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2651,51 +2651,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133343519</v>
+        <v>133344404</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>93208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635993</v>
+        <v>635423</v>
       </c>
       <c r="R19" t="n">
-        <v>6999755</v>
+        <v>6999959</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2724,7 +2721,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2731,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,34 +2740,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2780,7 +2761,7 @@
         <v>133344397</v>
       </c>
       <c r="B20" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2884,48 +2865,51 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133344404</v>
+        <v>133343519</v>
       </c>
       <c r="B21" t="n">
-        <v>93206</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635423</v>
+        <v>635993</v>
       </c>
       <c r="R21" t="n">
-        <v>6999959</v>
+        <v>6999755</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2954,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,18 +2957,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2994,7 +2994,7 @@
         <v>133344396</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>133344391</v>
       </c>
       <c r="B23" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>133344374</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>133344375</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>133344388</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133344417</v>
+        <v>133344413</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3593,13 +3593,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635820</v>
+        <v>635804</v>
       </c>
       <c r="R27" t="n">
-        <v>6999730</v>
+        <v>6999795</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344413</v>
+        <v>133344417</v>
       </c>
       <c r="B28" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635804</v>
+        <v>635820</v>
       </c>
       <c r="R28" t="n">
-        <v>6999795</v>
+        <v>6999730</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3895,7 +3895,7 @@
         <v>133344398</v>
       </c>
       <c r="B30" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,46 +3999,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4046,13 +4037,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R31" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4081,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4091,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4103,6 +4094,21 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4119,37 +4125,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>99132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4157,13 +4172,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R32" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4192,7 +4207,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4202,7 +4217,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4214,21 +4229,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4248,7 +4248,7 @@
         <v>133344402</v>
       </c>
       <c r="B33" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>133343517</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>133344418</v>
       </c>
       <c r="B37" t="n">
-        <v>89300</v>
+        <v>89302</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133343536</v>
+        <v>133344389</v>
       </c>
       <c r="B38" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4867,7 +4867,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4877,13 +4877,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635415</v>
+        <v>635661</v>
       </c>
       <c r="R38" t="n">
-        <v>6999961</v>
+        <v>6999959</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4937,12 +4937,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4952,7 +4952,7 @@
         <v>133343548</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>133344407</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133344389</v>
+        <v>133343536</v>
       </c>
       <c r="B41" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,16 +5193,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5215,7 +5215,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635661</v>
+        <v>635415</v>
       </c>
       <c r="R41" t="n">
-        <v>6999959</v>
+        <v>6999961</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5285,72 +5285,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>92219</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R42" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5379,7 +5367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5389,7 +5377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5398,67 +5386,78 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B43" t="n">
-        <v>92217</v>
+        <v>99132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R43" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5487,7 +5486,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,7 +5496,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5506,18 +5505,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5527,7 +5527,7 @@
         <v>133344395</v>
       </c>
       <c r="B44" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>133344421</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>133344412</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>133343547</v>
       </c>
       <c r="B47" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>133343551</v>
       </c>
       <c r="B48" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6354,45 +6354,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566448</v>
+        <v>133566388</v>
       </c>
       <c r="B51" t="n">
-        <v>80466</v>
+        <v>57955</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635576</v>
+        <v>635934</v>
       </c>
       <c r="R51" t="n">
-        <v>7000018</v>
+        <v>6999625</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6424,7 +6432,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6442,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6461,53 +6469,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566388</v>
+        <v>133566448</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>80467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635934</v>
+        <v>635576</v>
       </c>
       <c r="R52" t="n">
-        <v>6999625</v>
+        <v>7000018</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6694,7 +6694,7 @@
         <v>133566383</v>
       </c>
       <c r="B54" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6817,60 +6817,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>79334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R55" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6899,7 +6890,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6909,7 +6900,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6921,6 +6912,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6937,51 +6943,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B56" t="n">
-        <v>79333</v>
+        <v>99132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R56" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7010,7 +7025,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7020,7 +7035,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7032,21 +7047,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133344376</v>
+        <v>133344378</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>91883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635914</v>
+        <v>635862</v>
       </c>
       <c r="R2" t="n">
-        <v>6999854</v>
+        <v>6999958</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,45 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133344378</v>
+        <v>133344376</v>
       </c>
       <c r="B3" t="n">
-        <v>91883</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635862</v>
+        <v>635914</v>
       </c>
       <c r="R3" t="n">
-        <v>6999958</v>
+        <v>6999854</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133344406</v>
+        <v>133343516</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,37 +2199,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635433</v>
+        <v>636049</v>
       </c>
       <c r="R15" t="n">
-        <v>6999899</v>
+        <v>6999689</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2258,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,28 +2280,44 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133343516</v>
+        <v>133344406</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,40 +2325,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636049</v>
+        <v>635433</v>
       </c>
       <c r="R16" t="n">
-        <v>6999689</v>
+        <v>6999899</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2368,7 +2384,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2394,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,34 +2403,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133344378</v>
+        <v>133344376</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635862</v>
+        <v>635914</v>
       </c>
       <c r="R2" t="n">
-        <v>6999958</v>
+        <v>6999854</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133344376</v>
+        <v>133344378</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>91883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635914</v>
+        <v>635862</v>
       </c>
       <c r="R3" t="n">
-        <v>6999854</v>
+        <v>6999958</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133343516</v>
+        <v>133344406</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,40 +2199,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636049</v>
+        <v>635433</v>
       </c>
       <c r="R15" t="n">
-        <v>6999689</v>
+        <v>6999899</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2261,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,44 +2277,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133344406</v>
+        <v>133343516</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,37 +2306,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635433</v>
+        <v>636049</v>
       </c>
       <c r="R16" t="n">
-        <v>6999899</v>
+        <v>6999689</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2384,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2394,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,18 +2387,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -5297,48 +5297,60 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B42" t="n">
-        <v>92219</v>
+        <v>99132</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R42" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5367,7 +5379,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5386,78 +5398,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B43" t="n">
-        <v>99132</v>
+        <v>92219</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R43" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5496,7 +5497,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,19 +5506,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>133344378</v>
       </c>
       <c r="B3" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>133344424</v>
       </c>
       <c r="B5" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133344394</v>
+        <v>133344393</v>
       </c>
       <c r="B6" t="n">
-        <v>80399</v>
+        <v>80475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635695</v>
+        <v>635694</v>
       </c>
       <c r="R6" t="n">
-        <v>6999912</v>
+        <v>6999911</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1256,48 +1256,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133344393</v>
+        <v>133344405</v>
       </c>
       <c r="B7" t="n">
-        <v>80475</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635694</v>
+        <v>635419</v>
       </c>
       <c r="R7" t="n">
-        <v>6999911</v>
+        <v>6999913</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1329,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,24 +1345,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,45 +1363,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133344405</v>
+        <v>133344394</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>80399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635419</v>
+        <v>635695</v>
       </c>
       <c r="R8" t="n">
-        <v>6999913</v>
+        <v>6999912</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1452,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,8 +1455,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1492,7 +1492,7 @@
         <v>133343521</v>
       </c>
       <c r="B9" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>133343546</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>133344419</v>
       </c>
       <c r="B13" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>133344399</v>
       </c>
       <c r="B14" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>133344406</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2651,32 +2651,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133344404</v>
+        <v>133344397</v>
       </c>
       <c r="B19" t="n">
-        <v>93208</v>
+        <v>91928</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635423</v>
+        <v>635665</v>
       </c>
       <c r="R19" t="n">
-        <v>6999959</v>
+        <v>6999867</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2758,32 +2758,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133344397</v>
+        <v>133344404</v>
       </c>
       <c r="B20" t="n">
-        <v>91920</v>
+        <v>93216</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635665</v>
+        <v>635423</v>
       </c>
       <c r="R20" t="n">
-        <v>6999867</v>
+        <v>6999959</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,51 +2865,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133343519</v>
+        <v>133344396</v>
       </c>
       <c r="B21" t="n">
-        <v>91920</v>
+        <v>91891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635993</v>
+        <v>635669</v>
       </c>
       <c r="R21" t="n">
-        <v>6999755</v>
+        <v>6999875</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2938,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,82 +2954,69 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344396</v>
+        <v>133343519</v>
       </c>
       <c r="B22" t="n">
-        <v>91883</v>
+        <v>91928</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635669</v>
+        <v>635993</v>
       </c>
       <c r="R22" t="n">
-        <v>6999875</v>
+        <v>6999755</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3061,7 +3045,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3055,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,18 +3064,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133344374</v>
+        <v>133344375</v>
       </c>
       <c r="B24" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,21 +3235,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635973</v>
+        <v>635987</v>
       </c>
       <c r="R24" t="n">
-        <v>6999760</v>
+        <v>6999806</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3331,10 +3331,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344375</v>
+        <v>133344374</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3342,21 +3342,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635987</v>
+        <v>635973</v>
       </c>
       <c r="R25" t="n">
-        <v>6999806</v>
+        <v>6999760</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3441,7 +3441,7 @@
         <v>133344388</v>
       </c>
       <c r="B26" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133344413</v>
+        <v>133343549</v>
       </c>
       <c r="B27" t="n">
-        <v>91920</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,37 +3569,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635804</v>
+        <v>635842</v>
       </c>
       <c r="R27" t="n">
-        <v>6999795</v>
+        <v>6999727</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3636,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3646,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,22 +3666,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344417</v>
+        <v>133344413</v>
       </c>
       <c r="B28" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,13 +3713,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635820</v>
+        <v>635804</v>
       </c>
       <c r="R28" t="n">
-        <v>6999730</v>
+        <v>6999795</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,7 +3748,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3758,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,10 +3785,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133343549</v>
+        <v>133344417</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,45 +3796,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635842</v>
+        <v>635820</v>
       </c>
       <c r="R29" t="n">
-        <v>6999727</v>
+        <v>6999730</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3850,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3860,12 +3865,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3895,7 +3895,7 @@
         <v>133344398</v>
       </c>
       <c r="B30" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,37 +3999,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4037,13 +4046,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R31" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4072,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4094,21 +4103,6 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4125,46 +4119,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B32" t="n">
-        <v>99132</v>
+        <v>79334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4172,13 +4157,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R32" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4207,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4202,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4229,6 +4214,21 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4730,7 +4730,7 @@
         <v>133344418</v>
       </c>
       <c r="B37" t="n">
-        <v>89302</v>
+        <v>89310</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133344389</v>
+        <v>133344407</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>79334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4845,31 +4845,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4877,10 +4872,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635661</v>
+        <v>635393</v>
       </c>
       <c r="R38" t="n">
-        <v>6999959</v>
+        <v>6999887</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4912,7 +4907,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4922,7 +4917,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4931,8 +4926,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4949,10 +4960,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133343548</v>
+        <v>133344389</v>
       </c>
       <c r="B39" t="n">
-        <v>79334</v>
+        <v>57136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,37 +4971,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635839</v>
+        <v>635661</v>
       </c>
       <c r="R39" t="n">
-        <v>6999729</v>
+        <v>6999959</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5019,7 +5038,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5029,7 +5048,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5044,19 +5063,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133344407</v>
+        <v>133343548</v>
       </c>
       <c r="B40" t="n">
         <v>79334</v>
@@ -5085,22 +5104,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635393</v>
+        <v>635839</v>
       </c>
       <c r="R40" t="n">
-        <v>6999887</v>
+        <v>6999729</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5129,7 +5145,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5139,7 +5155,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5148,34 +5164,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5300,7 +5300,7 @@
         <v>133344423</v>
       </c>
       <c r="B42" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>133343518</v>
       </c>
       <c r="B43" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>133344395</v>
       </c>
       <c r="B44" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5864,10 +5864,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133343547</v>
+        <v>133344422</v>
       </c>
       <c r="B47" t="n">
-        <v>91920</v>
+        <v>57136</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5875,26 +5875,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5902,13 +5907,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635812</v>
+        <v>635832</v>
       </c>
       <c r="R47" t="n">
-        <v>6999735</v>
+        <v>6999733</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5937,7 +5942,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5947,7 +5952,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5956,85 +5961,82 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133343551</v>
+        <v>133344377</v>
       </c>
       <c r="B48" t="n">
-        <v>91883</v>
+        <v>58119</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635870</v>
+        <v>635919</v>
       </c>
       <c r="R48" t="n">
-        <v>6999720</v>
+        <v>6999871</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6063,7 +6065,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6073,7 +6075,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6082,76 +6084,55 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133344422</v>
+        <v>133343551</v>
       </c>
       <c r="B49" t="n">
-        <v>57136</v>
+        <v>91891</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6159,13 +6140,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635832</v>
+        <v>635870</v>
       </c>
       <c r="R49" t="n">
-        <v>6999733</v>
+        <v>6999720</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6194,7 +6175,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6204,7 +6185,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6213,28 +6194,44 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133344377</v>
+        <v>133343547</v>
       </c>
       <c r="B50" t="n">
-        <v>58119</v>
+        <v>91928</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6242,53 +6239,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635919</v>
+        <v>635812</v>
       </c>
       <c r="R50" t="n">
-        <v>6999871</v>
+        <v>6999735</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6317,7 +6301,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6327,7 +6311,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6336,71 +6320,79 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566388</v>
+        <v>133566448</v>
       </c>
       <c r="B51" t="n">
-        <v>57955</v>
+        <v>80467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635934</v>
+        <v>635576</v>
       </c>
       <c r="R51" t="n">
-        <v>6999625</v>
+        <v>7000018</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6432,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6442,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6469,45 +6461,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566448</v>
+        <v>133566388</v>
       </c>
       <c r="B52" t="n">
-        <v>80467</v>
+        <v>57955</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635576</v>
+        <v>635934</v>
       </c>
       <c r="R52" t="n">
-        <v>7000018</v>
+        <v>6999625</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6946,7 +6946,7 @@
         <v>133573160</v>
       </c>
       <c r="B56" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133343549</v>
+        <v>133344413</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,45 +3569,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635842</v>
+        <v>635804</v>
       </c>
       <c r="R27" t="n">
-        <v>6999727</v>
+        <v>6999795</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3636,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3646,12 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,19 +3653,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344413</v>
+        <v>133344417</v>
       </c>
       <c r="B28" t="n">
         <v>91928</v>
@@ -3713,13 +3700,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635804</v>
+        <v>635820</v>
       </c>
       <c r="R28" t="n">
-        <v>6999795</v>
+        <v>6999730</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3748,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3758,7 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,10 +3772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133344417</v>
+        <v>133343549</v>
       </c>
       <c r="B29" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,37 +3783,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635820</v>
+        <v>635842</v>
       </c>
       <c r="R29" t="n">
-        <v>6999730</v>
+        <v>6999727</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3855,7 +3850,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3860,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3999,46 +3999,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B31" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4046,13 +4037,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R31" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4081,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4091,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4103,6 +4094,21 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4119,37 +4125,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B32" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4157,13 +4172,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R32" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4192,7 +4207,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4202,7 +4217,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4214,21 +4229,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4245,10 +4245,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133344402</v>
+        <v>133343517</v>
       </c>
       <c r="B33" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635439</v>
+        <v>636054</v>
       </c>
       <c r="R33" t="n">
-        <v>6999963</v>
+        <v>6999703</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,38 +4343,38 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133343517</v>
+        <v>133344402</v>
       </c>
       <c r="B34" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4409,13 +4409,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636054</v>
+        <v>635439</v>
       </c>
       <c r="R34" t="n">
-        <v>6999703</v>
+        <v>6999963</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4469,38 +4469,38 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R35" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B36" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R36" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133344389</v>
+        <v>133343548</v>
       </c>
       <c r="B39" t="n">
-        <v>57136</v>
+        <v>79334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4971,45 +4971,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635661</v>
+        <v>635839</v>
       </c>
       <c r="R39" t="n">
-        <v>6999959</v>
+        <v>6999729</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5038,7 +5030,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5048,7 +5040,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5063,22 +5055,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133343548</v>
+        <v>133344389</v>
       </c>
       <c r="B40" t="n">
-        <v>79334</v>
+        <v>57136</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,37 +5078,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635839</v>
+        <v>635661</v>
       </c>
       <c r="R40" t="n">
-        <v>6999729</v>
+        <v>6999959</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5170,12 +5170,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5297,60 +5297,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B42" t="n">
-        <v>99140</v>
+        <v>92227</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R42" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5379,7 +5367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5389,7 +5377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5398,67 +5386,78 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B43" t="n">
-        <v>92227</v>
+        <v>99140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R43" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5487,7 +5486,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,7 +5496,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5506,18 +5505,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5864,42 +5864,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133344422</v>
+        <v>133343551</v>
       </c>
       <c r="B47" t="n">
-        <v>57136</v>
+        <v>91891</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5907,13 +5902,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635832</v>
+        <v>635870</v>
       </c>
       <c r="R47" t="n">
-        <v>6999733</v>
+        <v>6999720</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5942,7 +5937,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5952,7 +5947,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5961,28 +5956,44 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133344377</v>
+        <v>133343547</v>
       </c>
       <c r="B48" t="n">
-        <v>58119</v>
+        <v>91928</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5990,53 +6001,40 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635919</v>
+        <v>635812</v>
       </c>
       <c r="R48" t="n">
-        <v>6999871</v>
+        <v>6999735</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6065,7 +6063,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6075,7 +6073,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6084,55 +6082,76 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133343551</v>
+        <v>133344422</v>
       </c>
       <c r="B49" t="n">
-        <v>91891</v>
+        <v>57136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6140,13 +6159,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635870</v>
+        <v>635832</v>
       </c>
       <c r="R49" t="n">
-        <v>6999720</v>
+        <v>6999733</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6175,7 +6194,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6185,7 +6204,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6194,44 +6213,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133343547</v>
+        <v>133344377</v>
       </c>
       <c r="B50" t="n">
-        <v>91928</v>
+        <v>58119</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6239,40 +6242,53 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635812</v>
+        <v>635919</v>
       </c>
       <c r="R50" t="n">
-        <v>6999735</v>
+        <v>6999871</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6301,7 +6317,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6311,7 +6327,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6320,34 +6336,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6817,51 +6817,60 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R55" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6890,7 +6899,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6900,7 +6909,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6912,21 +6921,6 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6943,60 +6937,51 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B56" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R56" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7025,7 +7010,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7035,7 +7020,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7047,6 +7032,21 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133344413</v>
+        <v>133343549</v>
       </c>
       <c r="B27" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,37 +3569,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635804</v>
+        <v>635842</v>
       </c>
       <c r="R27" t="n">
-        <v>6999795</v>
+        <v>6999727</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3636,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3646,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,19 +3666,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344417</v>
+        <v>133344413</v>
       </c>
       <c r="B28" t="n">
         <v>91928</v>
@@ -3700,13 +3713,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635820</v>
+        <v>635804</v>
       </c>
       <c r="R28" t="n">
-        <v>6999730</v>
+        <v>6999795</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,7 +3748,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3758,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,10 +3785,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133343549</v>
+        <v>133344417</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,45 +3796,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635842</v>
+        <v>635820</v>
       </c>
       <c r="R29" t="n">
-        <v>6999727</v>
+        <v>6999730</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3850,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3860,12 +3865,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3999,37 +3999,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4037,13 +4046,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R31" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4072,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4094,21 +4103,6 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4125,46 +4119,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B32" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4172,13 +4157,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R32" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4207,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4202,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4229,6 +4214,21 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B35" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R35" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B36" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R36" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -6817,60 +6817,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B55" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R55" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6899,7 +6890,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6909,7 +6900,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6921,6 +6912,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6937,51 +6943,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B56" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R56" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7010,7 +7025,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7020,7 +7035,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7032,21 +7047,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -3224,10 +3224,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133344375</v>
+        <v>133344374</v>
       </c>
       <c r="B24" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,21 +3235,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635987</v>
+        <v>635973</v>
       </c>
       <c r="R24" t="n">
-        <v>6999806</v>
+        <v>6999760</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3331,45 +3331,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344374</v>
+        <v>133344388</v>
       </c>
       <c r="B25" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635973</v>
+        <v>635662</v>
       </c>
       <c r="R25" t="n">
-        <v>6999760</v>
+        <v>6999959</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3401,7 +3413,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3411,7 +3423,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,6 +3432,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3438,57 +3451,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133344388</v>
+        <v>133344375</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635662</v>
+        <v>635987</v>
       </c>
       <c r="R26" t="n">
-        <v>6999959</v>
+        <v>6999806</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3520,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,7 +3540,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133343549</v>
+        <v>133344413</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,45 +3569,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635842</v>
+        <v>635804</v>
       </c>
       <c r="R27" t="n">
-        <v>6999727</v>
+        <v>6999795</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3636,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3646,12 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,19 +3653,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344413</v>
+        <v>133344417</v>
       </c>
       <c r="B28" t="n">
         <v>91928</v>
@@ -3713,13 +3700,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635804</v>
+        <v>635820</v>
       </c>
       <c r="R28" t="n">
-        <v>6999795</v>
+        <v>6999730</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3748,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3758,7 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,10 +3772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133344417</v>
+        <v>133343549</v>
       </c>
       <c r="B29" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,37 +3783,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635820</v>
+        <v>635842</v>
       </c>
       <c r="R29" t="n">
-        <v>6999730</v>
+        <v>6999727</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3855,7 +3850,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3860,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3999,46 +3999,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B31" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4046,13 +4037,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R31" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4081,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4091,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4103,6 +4094,21 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4119,37 +4125,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B32" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4157,13 +4172,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R32" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4192,7 +4207,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4202,7 +4217,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4214,21 +4229,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R35" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B36" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R36" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133344413</v>
+        <v>133343549</v>
       </c>
       <c r="B27" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,37 +3569,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635804</v>
+        <v>635842</v>
       </c>
       <c r="R27" t="n">
-        <v>6999795</v>
+        <v>6999727</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3636,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3646,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,19 +3666,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344417</v>
+        <v>133344413</v>
       </c>
       <c r="B28" t="n">
         <v>91928</v>
@@ -3700,13 +3713,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635820</v>
+        <v>635804</v>
       </c>
       <c r="R28" t="n">
-        <v>6999730</v>
+        <v>6999795</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,7 +3748,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3758,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,10 +3785,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133343549</v>
+        <v>133344417</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,45 +3796,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635842</v>
+        <v>635820</v>
       </c>
       <c r="R29" t="n">
-        <v>6999727</v>
+        <v>6999730</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3850,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3860,12 +3865,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B35" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R35" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B36" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R36" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5297,48 +5297,60 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B42" t="n">
-        <v>92227</v>
+        <v>99140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R42" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5367,7 +5379,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5386,78 +5398,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B43" t="n">
-        <v>99140</v>
+        <v>92227</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R43" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5496,7 +5497,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,19 +5506,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6817,51 +6817,60 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R55" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6890,7 +6899,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6900,7 +6909,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6912,21 +6921,6 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6943,60 +6937,51 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B56" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R56" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7025,7 +7010,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7035,7 +7020,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7047,6 +7032,21 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133344376</v>
+        <v>133344378</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635914</v>
+        <v>635862</v>
       </c>
       <c r="R2" t="n">
-        <v>6999854</v>
+        <v>6999958</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,45 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133344378</v>
+        <v>133344376</v>
       </c>
       <c r="B3" t="n">
-        <v>91891</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635862</v>
+        <v>635914</v>
       </c>
       <c r="R3" t="n">
-        <v>6999958</v>
+        <v>6999854</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R35" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B36" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R36" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5297,60 +5297,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B42" t="n">
-        <v>99140</v>
+        <v>92227</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R42" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5379,7 +5367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5389,7 +5377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5398,67 +5386,78 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B43" t="n">
-        <v>92227</v>
+        <v>99140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R43" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5487,7 +5486,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,7 +5496,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5506,18 +5505,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6354,45 +6354,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566448</v>
+        <v>133566388</v>
       </c>
       <c r="B51" t="n">
-        <v>80467</v>
+        <v>57955</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635576</v>
+        <v>635934</v>
       </c>
       <c r="R51" t="n">
-        <v>7000018</v>
+        <v>6999625</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6424,7 +6432,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6442,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6461,7 +6469,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566388</v>
+        <v>133566389</v>
       </c>
       <c r="B52" t="n">
         <v>57955</v>
@@ -6504,10 +6512,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635934</v>
+        <v>635931</v>
       </c>
       <c r="R52" t="n">
-        <v>6999625</v>
+        <v>6999628</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6539,7 +6547,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6549,7 +6557,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6576,53 +6584,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133566389</v>
+        <v>133566448</v>
       </c>
       <c r="B53" t="n">
-        <v>57955</v>
+        <v>80467</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635931</v>
+        <v>635576</v>
       </c>
       <c r="R53" t="n">
-        <v>6999628</v>
+        <v>7000018</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6817,60 +6817,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B55" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R55" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6899,7 +6890,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6909,7 +6900,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6921,6 +6912,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6937,51 +6943,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B56" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R56" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7010,7 +7025,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7020,7 +7035,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7032,21 +7047,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133344378</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133344376</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>133344392</v>
       </c>
       <c r="B4" t="n">
-        <v>80474</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>133344424</v>
       </c>
       <c r="B5" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>133344393</v>
       </c>
       <c r="B6" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,45 +1256,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133344405</v>
+        <v>133344394</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>80413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635419</v>
+        <v>635695</v>
       </c>
       <c r="R7" t="n">
-        <v>6999913</v>
+        <v>6999912</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1326,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,8 +1348,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1363,48 +1382,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133344394</v>
+        <v>133344405</v>
       </c>
       <c r="B8" t="n">
-        <v>80399</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635695</v>
+        <v>635419</v>
       </c>
       <c r="R8" t="n">
-        <v>6999912</v>
+        <v>6999913</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1436,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,24 +1471,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133343521</v>
+        <v>133343546</v>
       </c>
       <c r="B9" t="n">
-        <v>92227</v>
+        <v>91947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,34 +1500,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635861</v>
+        <v>635817</v>
       </c>
       <c r="R9" t="n">
-        <v>6999964</v>
+        <v>6999735</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1559,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,8 +1581,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133343546</v>
+        <v>133343521</v>
       </c>
       <c r="B10" t="n">
-        <v>91928</v>
+        <v>92218</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,37 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635817</v>
+        <v>635861</v>
       </c>
       <c r="R10" t="n">
-        <v>6999735</v>
+        <v>6999964</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1669,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,24 +1704,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1725,7 +1725,7 @@
         <v>133343520</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,51 +1848,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133343545</v>
+        <v>133344399</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>91910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635836</v>
+        <v>635669</v>
       </c>
       <c r="R12" t="n">
-        <v>6999746</v>
+        <v>6999846</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,34 +1937,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1977,7 +1958,7 @@
         <v>133344419</v>
       </c>
       <c r="B13" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,48 +2062,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133344399</v>
+        <v>133343545</v>
       </c>
       <c r="B14" t="n">
-        <v>91891</v>
+        <v>79348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635669</v>
+        <v>635836</v>
       </c>
       <c r="R14" t="n">
-        <v>6999846</v>
+        <v>6999746</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2151,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,28 +2154,44 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133344406</v>
+        <v>133343516</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,37 +2199,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635433</v>
+        <v>636049</v>
       </c>
       <c r="R15" t="n">
-        <v>6999899</v>
+        <v>6999689</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2258,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,28 +2280,44 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133343516</v>
+        <v>133344410</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>57962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,26 +2325,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2333,13 +2357,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636049</v>
+        <v>635570</v>
       </c>
       <c r="R16" t="n">
-        <v>6999689</v>
+        <v>6999790</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2368,7 +2392,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2402,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,44 +2411,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133344410</v>
+        <v>133344406</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>91947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,42 +2440,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635570</v>
+        <v>635433</v>
       </c>
       <c r="R17" t="n">
-        <v>6999790</v>
+        <v>6999899</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,7 +2539,7 @@
         <v>133343531</v>
       </c>
       <c r="B18" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133344397</v>
+        <v>133343519</v>
       </c>
       <c r="B19" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,19 +2680,22 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635665</v>
+        <v>635993</v>
       </c>
       <c r="R19" t="n">
-        <v>6999867</v>
+        <v>6999755</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2721,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,28 +2743,44 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133344404</v>
+        <v>133344396</v>
       </c>
       <c r="B20" t="n">
-        <v>93216</v>
+        <v>91910</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,21 +2788,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2793,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635423</v>
+        <v>635669</v>
       </c>
       <c r="R20" t="n">
-        <v>6999959</v>
+        <v>6999875</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2828,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,32 +2884,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133344396</v>
+        <v>133344397</v>
       </c>
       <c r="B21" t="n">
-        <v>91891</v>
+        <v>91947</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2900,10 +2919,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635669</v>
+        <v>635665</v>
       </c>
       <c r="R21" t="n">
-        <v>6999875</v>
+        <v>6999867</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2935,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,51 +2991,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133343519</v>
+        <v>133344404</v>
       </c>
       <c r="B22" t="n">
-        <v>91928</v>
+        <v>93244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635993</v>
+        <v>635423</v>
       </c>
       <c r="R22" t="n">
-        <v>6999755</v>
+        <v>6999959</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3045,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3055,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,34 +3080,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
         <v>133344391</v>
       </c>
       <c r="B23" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>133344374</v>
       </c>
       <c r="B24" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>133344388</v>
       </c>
       <c r="B25" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>133344375</v>
       </c>
       <c r="B26" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>133343549</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344413</v>
+        <v>133344417</v>
       </c>
       <c r="B28" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635804</v>
+        <v>635820</v>
       </c>
       <c r="R28" t="n">
-        <v>6999795</v>
+        <v>6999730</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,10 +3785,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133344417</v>
+        <v>133344413</v>
       </c>
       <c r="B29" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,13 +3820,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635820</v>
+        <v>635804</v>
       </c>
       <c r="R29" t="n">
-        <v>6999730</v>
+        <v>6999795</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,7 +3895,7 @@
         <v>133344398</v>
       </c>
       <c r="B30" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,37 +3999,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>99168</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4037,13 +4046,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R31" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4072,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4094,21 +4103,6 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4125,46 +4119,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B32" t="n">
-        <v>99140</v>
+        <v>79348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4172,13 +4157,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R32" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4207,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4202,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4229,6 +4214,21 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4248,7 +4248,7 @@
         <v>133343517</v>
       </c>
       <c r="B33" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>133344402</v>
       </c>
       <c r="B34" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B35" t="n">
-        <v>57136</v>
+        <v>57962</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R35" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B36" t="n">
-        <v>57955</v>
+        <v>57143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R36" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4730,7 +4730,7 @@
         <v>133344418</v>
       </c>
       <c r="B37" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>133344407</v>
       </c>
       <c r="B38" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133343548</v>
+        <v>133344389</v>
       </c>
       <c r="B39" t="n">
-        <v>79334</v>
+        <v>57143</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4971,37 +4971,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635839</v>
+        <v>635661</v>
       </c>
       <c r="R39" t="n">
-        <v>6999729</v>
+        <v>6999959</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5030,7 +5038,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5040,7 +5048,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5055,22 +5063,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133344389</v>
+        <v>133343548</v>
       </c>
       <c r="B40" t="n">
-        <v>57136</v>
+        <v>79348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,45 +5086,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635661</v>
+        <v>635839</v>
       </c>
       <c r="R40" t="n">
-        <v>6999959</v>
+        <v>6999729</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5170,12 +5170,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5185,7 +5185,7 @@
         <v>133343536</v>
       </c>
       <c r="B41" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5297,48 +5297,60 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B42" t="n">
-        <v>92227</v>
+        <v>99168</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R42" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5367,7 +5379,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5386,78 +5398,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B43" t="n">
-        <v>99140</v>
+        <v>92218</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R43" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5496,7 +5497,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,29 +5506,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133344395</v>
+        <v>133344421</v>
       </c>
       <c r="B44" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635671</v>
+        <v>635821</v>
       </c>
       <c r="R44" t="n">
-        <v>6999877</v>
+        <v>6999726</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133344421</v>
+        <v>133344395</v>
       </c>
       <c r="B45" t="n">
-        <v>79334</v>
+        <v>91947</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635821</v>
+        <v>635671</v>
       </c>
       <c r="R45" t="n">
-        <v>6999726</v>
+        <v>6999877</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5741,7 +5741,7 @@
         <v>133344412</v>
       </c>
       <c r="B46" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5864,32 +5864,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133343551</v>
+        <v>133343547</v>
       </c>
       <c r="B47" t="n">
-        <v>91891</v>
+        <v>91947</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635870</v>
+        <v>635812</v>
       </c>
       <c r="R47" t="n">
-        <v>6999720</v>
+        <v>6999735</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5990,32 +5990,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133343547</v>
+        <v>133343551</v>
       </c>
       <c r="B48" t="n">
-        <v>91928</v>
+        <v>91910</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635812</v>
+        <v>635870</v>
       </c>
       <c r="R48" t="n">
-        <v>6999735</v>
+        <v>6999720</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6119,7 +6119,7 @@
         <v>133344422</v>
       </c>
       <c r="B49" t="n">
-        <v>57136</v>
+        <v>57143</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>133344377</v>
       </c>
       <c r="B50" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6354,53 +6354,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566388</v>
+        <v>133566448</v>
       </c>
       <c r="B51" t="n">
-        <v>57955</v>
+        <v>80481</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635934</v>
+        <v>635576</v>
       </c>
       <c r="R51" t="n">
-        <v>6999625</v>
+        <v>7000018</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6432,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6442,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6469,10 +6461,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566389</v>
+        <v>133566388</v>
       </c>
       <c r="B52" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6512,10 +6504,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635931</v>
+        <v>635934</v>
       </c>
       <c r="R52" t="n">
-        <v>6999628</v>
+        <v>6999625</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6547,7 +6539,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6557,7 +6549,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6584,45 +6576,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133566448</v>
+        <v>133566389</v>
       </c>
       <c r="B53" t="n">
-        <v>80467</v>
+        <v>57962</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635576</v>
+        <v>635931</v>
       </c>
       <c r="R53" t="n">
-        <v>7000018</v>
+        <v>6999628</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6694,7 +6694,7 @@
         <v>133566383</v>
       </c>
       <c r="B54" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6817,51 +6817,60 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>99168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R55" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6890,7 +6899,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6900,7 +6909,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6912,21 +6921,6 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6943,60 +6937,51 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B56" t="n">
-        <v>99140</v>
+        <v>79348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R56" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7025,7 +7010,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7035,7 +7020,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7047,6 +7032,21 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133344393</v>
+        <v>133344394</v>
       </c>
       <c r="B6" t="n">
-        <v>80489</v>
+        <v>80413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635694</v>
+        <v>635695</v>
       </c>
       <c r="R6" t="n">
-        <v>6999911</v>
+        <v>6999912</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133344394</v>
+        <v>133344393</v>
       </c>
       <c r="B7" t="n">
-        <v>80413</v>
+        <v>80489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635695</v>
+        <v>635694</v>
       </c>
       <c r="R7" t="n">
-        <v>6999912</v>
+        <v>6999911</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133343546</v>
+        <v>133343521</v>
       </c>
       <c r="B9" t="n">
-        <v>91947</v>
+        <v>92218</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,37 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635817</v>
+        <v>635861</v>
       </c>
       <c r="R9" t="n">
-        <v>6999735</v>
+        <v>6999964</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1562,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,24 +1578,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1615,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133343521</v>
+        <v>133343546</v>
       </c>
       <c r="B10" t="n">
-        <v>92218</v>
+        <v>91947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,34 +1607,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635861</v>
+        <v>635817</v>
       </c>
       <c r="R10" t="n">
-        <v>6999964</v>
+        <v>6999735</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,8 +1688,24 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1848,7 +1848,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133344399</v>
+        <v>133344419</v>
       </c>
       <c r="B12" t="n">
         <v>91910</v>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635669</v>
+        <v>635818</v>
       </c>
       <c r="R12" t="n">
-        <v>6999846</v>
+        <v>6999728</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,7 +1955,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133344419</v>
+        <v>133344399</v>
       </c>
       <c r="B13" t="n">
         <v>91910</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635818</v>
+        <v>635669</v>
       </c>
       <c r="R13" t="n">
-        <v>6999728</v>
+        <v>6999846</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2188,37 +2188,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133343516</v>
+        <v>133343531</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>57152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2226,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636049</v>
+        <v>635688</v>
       </c>
       <c r="R15" t="n">
-        <v>6999689</v>
+        <v>6999888</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2261,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,24 +2285,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2314,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133344410</v>
+        <v>133343516</v>
       </c>
       <c r="B16" t="n">
-        <v>57962</v>
+        <v>79348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,31 +2314,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2357,13 +2341,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635570</v>
+        <v>636049</v>
       </c>
       <c r="R16" t="n">
-        <v>6999790</v>
+        <v>6999689</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,7 +2386,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,18 +2395,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2536,32 +2536,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133343531</v>
+        <v>133344410</v>
       </c>
       <c r="B18" t="n">
-        <v>57152</v>
+        <v>57962</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2569,7 +2569,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2579,13 +2579,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635688</v>
+        <v>635570</v>
       </c>
       <c r="R18" t="n">
-        <v>6999888</v>
+        <v>6999790</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,12 +2639,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2777,32 +2777,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133344396</v>
+        <v>133344397</v>
       </c>
       <c r="B20" t="n">
-        <v>91910</v>
+        <v>91947</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635669</v>
+        <v>635665</v>
       </c>
       <c r="R20" t="n">
-        <v>6999875</v>
+        <v>6999867</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,32 +2884,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133344397</v>
+        <v>133344404</v>
       </c>
       <c r="B21" t="n">
-        <v>91947</v>
+        <v>93244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635665</v>
+        <v>635423</v>
       </c>
       <c r="R21" t="n">
-        <v>6999867</v>
+        <v>6999959</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344404</v>
+        <v>133344396</v>
       </c>
       <c r="B22" t="n">
-        <v>93244</v>
+        <v>91910</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3002,21 +3002,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635423</v>
+        <v>635669</v>
       </c>
       <c r="R22" t="n">
-        <v>6999959</v>
+        <v>6999875</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3224,10 +3224,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133344374</v>
+        <v>133344375</v>
       </c>
       <c r="B24" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,21 +3235,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635973</v>
+        <v>635987</v>
       </c>
       <c r="R24" t="n">
-        <v>6999760</v>
+        <v>6999806</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3331,57 +3331,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133344388</v>
+        <v>133344374</v>
       </c>
       <c r="B25" t="n">
-        <v>99168</v>
+        <v>91947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635662</v>
+        <v>635973</v>
       </c>
       <c r="R25" t="n">
-        <v>6999959</v>
+        <v>6999760</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3413,7 +3401,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3423,7 +3411,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,7 +3420,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3451,45 +3438,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133344375</v>
+        <v>133344388</v>
       </c>
       <c r="B26" t="n">
-        <v>79348</v>
+        <v>99168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635987</v>
+        <v>635662</v>
       </c>
       <c r="R26" t="n">
-        <v>6999806</v>
+        <v>6999959</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3521,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3530,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,6 +3539,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133343549</v>
+        <v>133344413</v>
       </c>
       <c r="B27" t="n">
-        <v>57965</v>
+        <v>91947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,45 +3569,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635842</v>
+        <v>635804</v>
       </c>
       <c r="R27" t="n">
-        <v>6999727</v>
+        <v>6999795</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3636,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3646,12 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,12 +3653,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3785,10 +3772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133344413</v>
+        <v>133343549</v>
       </c>
       <c r="B29" t="n">
-        <v>91947</v>
+        <v>57965</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,37 +3783,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635804</v>
+        <v>635842</v>
       </c>
       <c r="R29" t="n">
-        <v>6999795</v>
+        <v>6999727</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3855,7 +3850,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3860,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,22 +3880,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133344398</v>
+        <v>133344416</v>
       </c>
       <c r="B30" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,34 +3903,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635670</v>
+        <v>635824</v>
       </c>
       <c r="R30" t="n">
-        <v>6999849</v>
+        <v>6999739</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -3962,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3972,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3981,8 +3984,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4119,10 +4138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344416</v>
+        <v>133344398</v>
       </c>
       <c r="B32" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4130,37 +4149,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635824</v>
+        <v>635670</v>
       </c>
       <c r="R32" t="n">
-        <v>6999739</v>
+        <v>6999849</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4192,7 +4208,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4202,7 +4218,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,24 +4227,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4245,10 +4245,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133343517</v>
+        <v>133344402</v>
       </c>
       <c r="B33" t="n">
-        <v>79348</v>
+        <v>80453</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636054</v>
+        <v>635439</v>
       </c>
       <c r="R33" t="n">
-        <v>6999703</v>
+        <v>6999963</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,38 +4343,38 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133344402</v>
+        <v>133343517</v>
       </c>
       <c r="B34" t="n">
-        <v>80453</v>
+        <v>79348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4409,13 +4409,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635439</v>
+        <v>636054</v>
       </c>
       <c r="R34" t="n">
-        <v>6999963</v>
+        <v>6999703</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4469,38 +4469,38 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B35" t="n">
-        <v>57962</v>
+        <v>57143</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R35" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B36" t="n">
-        <v>57143</v>
+        <v>57962</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R36" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133343548</v>
+        <v>133343536</v>
       </c>
       <c r="B40" t="n">
-        <v>79348</v>
+        <v>57962</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,34 +5086,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635839</v>
+        <v>635415</v>
       </c>
       <c r="R40" t="n">
-        <v>6999729</v>
+        <v>6999961</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5145,7 +5153,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5163,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5182,10 +5190,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133343536</v>
+        <v>133343548</v>
       </c>
       <c r="B41" t="n">
-        <v>57962</v>
+        <v>79348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,42 +5201,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635415</v>
+        <v>635839</v>
       </c>
       <c r="R41" t="n">
-        <v>6999961</v>
+        <v>6999729</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5297,60 +5297,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B42" t="n">
-        <v>99168</v>
+        <v>92218</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R42" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5379,7 +5367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5389,7 +5377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5398,67 +5386,78 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B43" t="n">
-        <v>92218</v>
+        <v>99168</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R43" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5487,7 +5486,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,7 +5496,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5506,28 +5505,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133344421</v>
+        <v>133344395</v>
       </c>
       <c r="B44" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5535,21 +5535,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635821</v>
+        <v>635671</v>
       </c>
       <c r="R44" t="n">
-        <v>6999726</v>
+        <v>6999877</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5631,10 +5631,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133344395</v>
+        <v>133344421</v>
       </c>
       <c r="B45" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635671</v>
+        <v>635821</v>
       </c>
       <c r="R45" t="n">
-        <v>6999877</v>
+        <v>6999726</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5864,32 +5864,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133343547</v>
+        <v>133343551</v>
       </c>
       <c r="B47" t="n">
-        <v>91947</v>
+        <v>91910</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635812</v>
+        <v>635870</v>
       </c>
       <c r="R47" t="n">
-        <v>6999735</v>
+        <v>6999720</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5990,32 +5990,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133343551</v>
+        <v>133343547</v>
       </c>
       <c r="B48" t="n">
-        <v>91910</v>
+        <v>91947</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635870</v>
+        <v>635812</v>
       </c>
       <c r="R48" t="n">
-        <v>6999720</v>
+        <v>6999735</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6116,10 +6116,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133344422</v>
+        <v>133344377</v>
       </c>
       <c r="B49" t="n">
-        <v>57143</v>
+        <v>58126</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6127,42 +6127,50 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635832</v>
+        <v>635919</v>
       </c>
       <c r="R49" t="n">
-        <v>6999733</v>
+        <v>6999871</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6194,7 +6202,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6204,7 +6212,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6231,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133344377</v>
+        <v>133344422</v>
       </c>
       <c r="B50" t="n">
-        <v>58126</v>
+        <v>57143</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6242,50 +6250,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635919</v>
+        <v>635832</v>
       </c>
       <c r="R50" t="n">
-        <v>6999871</v>
+        <v>6999733</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6817,60 +6817,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B55" t="n">
-        <v>99168</v>
+        <v>79348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R55" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6899,7 +6890,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6909,7 +6900,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6921,6 +6912,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6937,51 +6943,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B56" t="n">
-        <v>79348</v>
+        <v>99168</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R56" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7010,7 +7025,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7020,7 +7035,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7032,21 +7047,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133344378</v>
       </c>
       <c r="B2" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133344376</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>133344392</v>
       </c>
       <c r="B4" t="n">
-        <v>80488</v>
+        <v>80484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>133344424</v>
       </c>
       <c r="B5" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>133344394</v>
       </c>
       <c r="B6" t="n">
-        <v>80413</v>
+        <v>80423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>133344393</v>
       </c>
       <c r="B7" t="n">
-        <v>80489</v>
+        <v>80485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>133344405</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>133343521</v>
       </c>
       <c r="B9" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>133343546</v>
       </c>
       <c r="B10" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>133343520</v>
       </c>
       <c r="B11" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,48 +1848,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133344419</v>
+        <v>133343545</v>
       </c>
       <c r="B12" t="n">
-        <v>91910</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635818</v>
+        <v>635836</v>
       </c>
       <c r="R12" t="n">
-        <v>6999728</v>
+        <v>6999746</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1918,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,28 +1940,44 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133344399</v>
+        <v>133344419</v>
       </c>
       <c r="B13" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635669</v>
+        <v>635818</v>
       </c>
       <c r="R13" t="n">
-        <v>6999846</v>
+        <v>6999728</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2025,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2054,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,51 +2081,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133343545</v>
+        <v>133344399</v>
       </c>
       <c r="B14" t="n">
-        <v>79348</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635836</v>
+        <v>635669</v>
       </c>
       <c r="R14" t="n">
-        <v>6999746</v>
+        <v>6999846</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2135,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,34 +2170,18 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2191,7 +2191,7 @@
         <v>133343531</v>
       </c>
       <c r="B15" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>133343516</v>
       </c>
       <c r="B16" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>133344406</v>
       </c>
       <c r="B17" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>133344410</v>
       </c>
       <c r="B18" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133343519</v>
+        <v>133344397</v>
       </c>
       <c r="B19" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,22 +2680,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635993</v>
+        <v>635665</v>
       </c>
       <c r="R19" t="n">
-        <v>6999755</v>
+        <v>6999867</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2724,7 +2721,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2731,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,66 +2740,50 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133344397</v>
+        <v>133344404</v>
       </c>
       <c r="B20" t="n">
-        <v>91947</v>
+        <v>93254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2812,10 +2793,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635665</v>
+        <v>635423</v>
       </c>
       <c r="R20" t="n">
-        <v>6999867</v>
+        <v>6999959</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2847,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2857,7 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133344404</v>
+        <v>133344396</v>
       </c>
       <c r="B21" t="n">
-        <v>93244</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2919,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635423</v>
+        <v>635669</v>
       </c>
       <c r="R21" t="n">
-        <v>6999959</v>
+        <v>6999875</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2954,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,45 +2972,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344396</v>
+        <v>133344391</v>
       </c>
       <c r="B22" t="n">
-        <v>91910</v>
+        <v>80473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635669</v>
+        <v>635694</v>
       </c>
       <c r="R22" t="n">
-        <v>6999875</v>
+        <v>6999907</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3061,7 +3045,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3055,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,8 +3064,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133344391</v>
+        <v>133343519</v>
       </c>
       <c r="B23" t="n">
-        <v>80453</v>
+        <v>91957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635694</v>
+        <v>635993</v>
       </c>
       <c r="R23" t="n">
-        <v>6999907</v>
+        <v>6999755</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,28 +3196,28 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
         <v>133344375</v>
       </c>
       <c r="B24" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>133344374</v>
       </c>
       <c r="B25" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>133344388</v>
       </c>
       <c r="B26" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133344413</v>
+        <v>133343549</v>
       </c>
       <c r="B27" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,37 +3569,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635804</v>
+        <v>635842</v>
       </c>
       <c r="R27" t="n">
-        <v>6999795</v>
+        <v>6999727</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3636,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3646,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,22 +3666,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344417</v>
+        <v>133344413</v>
       </c>
       <c r="B28" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,13 +3713,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635820</v>
+        <v>635804</v>
       </c>
       <c r="R28" t="n">
-        <v>6999730</v>
+        <v>6999795</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,7 +3748,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3758,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,10 +3785,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133343549</v>
+        <v>133344417</v>
       </c>
       <c r="B29" t="n">
-        <v>57965</v>
+        <v>91957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,45 +3796,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635842</v>
+        <v>635820</v>
       </c>
       <c r="R29" t="n">
-        <v>6999727</v>
+        <v>6999730</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3850,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3860,12 +3865,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,49 +3880,58 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B30" t="n">
-        <v>79348</v>
+        <v>99178</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3930,13 +3939,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R30" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3965,7 +3974,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3984,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3987,21 +3996,6 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4018,60 +4012,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344390</v>
+        <v>133344398</v>
       </c>
       <c r="B31" t="n">
-        <v>99168</v>
+        <v>91957</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635693</v>
+        <v>635670</v>
       </c>
       <c r="R31" t="n">
-        <v>6999909</v>
+        <v>6999849</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,7 +4082,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4110,7 +4092,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4119,7 +4101,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4138,10 +4119,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344398</v>
+        <v>133344416</v>
       </c>
       <c r="B32" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4149,34 +4130,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635670</v>
+        <v>635824</v>
       </c>
       <c r="R32" t="n">
-        <v>6999849</v>
+        <v>6999739</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4208,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4218,7 +4202,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4227,8 +4211,24 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4248,7 +4248,7 @@
         <v>133344402</v>
       </c>
       <c r="B33" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>133343517</v>
       </c>
       <c r="B34" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133344386</v>
+        <v>133343537</v>
       </c>
       <c r="B35" t="n">
-        <v>57143</v>
+        <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4530,7 +4530,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4540,13 +4540,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>635624</v>
+        <v>635449</v>
       </c>
       <c r="R35" t="n">
-        <v>6999967</v>
+        <v>6999895</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4600,22 +4600,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133343537</v>
+        <v>133344386</v>
       </c>
       <c r="B36" t="n">
-        <v>57962</v>
+        <v>57153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>635449</v>
+        <v>635624</v>
       </c>
       <c r="R36" t="n">
-        <v>6999895</v>
+        <v>6999967</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,12 +4715,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4730,7 +4730,7 @@
         <v>133344418</v>
       </c>
       <c r="B37" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133344407</v>
+        <v>133343548</v>
       </c>
       <c r="B38" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4863,22 +4863,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635393</v>
+        <v>635839</v>
       </c>
       <c r="R38" t="n">
-        <v>6999887</v>
+        <v>6999729</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4907,7 +4904,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4917,7 +4914,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4926,44 +4923,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133344389</v>
+        <v>133343536</v>
       </c>
       <c r="B39" t="n">
-        <v>57143</v>
+        <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4971,16 +4952,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4993,7 +4974,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5003,13 +4984,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635661</v>
+        <v>635415</v>
       </c>
       <c r="R39" t="n">
-        <v>6999959</v>
+        <v>6999961</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5038,7 +5019,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5048,7 +5029,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5063,22 +5044,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133343536</v>
+        <v>133344407</v>
       </c>
       <c r="B40" t="n">
-        <v>57962</v>
+        <v>79358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,31 +5067,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5118,13 +5094,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635415</v>
+        <v>635393</v>
       </c>
       <c r="R40" t="n">
-        <v>6999961</v>
+        <v>6999887</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5153,7 +5129,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5163,7 +5139,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5172,28 +5148,44 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133343548</v>
+        <v>133344389</v>
       </c>
       <c r="B41" t="n">
-        <v>79348</v>
+        <v>57153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5201,37 +5193,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>635839</v>
+        <v>635661</v>
       </c>
       <c r="R41" t="n">
-        <v>6999729</v>
+        <v>6999959</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5285,60 +5285,72 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B42" t="n">
-        <v>92218</v>
+        <v>99178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R42" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5367,7 +5379,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5386,78 +5398,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B43" t="n">
-        <v>99168</v>
+        <v>92228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R43" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5496,7 +5497,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,19 +5506,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5527,7 +5527,7 @@
         <v>133344395</v>
       </c>
       <c r="B44" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>133344421</v>
       </c>
       <c r="B45" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>133344412</v>
       </c>
       <c r="B46" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5864,51 +5864,64 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133343551</v>
+        <v>133344377</v>
       </c>
       <c r="B47" t="n">
-        <v>91910</v>
+        <v>58136</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635870</v>
+        <v>635919</v>
       </c>
       <c r="R47" t="n">
-        <v>6999720</v>
+        <v>6999871</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5937,7 +5950,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5947,7 +5960,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5956,66 +5969,50 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133343547</v>
+        <v>133343551</v>
       </c>
       <c r="B48" t="n">
-        <v>91947</v>
+        <v>91920</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6028,10 +6025,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635812</v>
+        <v>635870</v>
       </c>
       <c r="R48" t="n">
-        <v>6999735</v>
+        <v>6999720</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6063,7 +6060,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6073,7 +6070,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6116,10 +6113,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133344377</v>
+        <v>133343547</v>
       </c>
       <c r="B49" t="n">
-        <v>58126</v>
+        <v>91957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6127,53 +6124,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635919</v>
+        <v>635812</v>
       </c>
       <c r="R49" t="n">
-        <v>6999871</v>
+        <v>6999735</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6202,7 +6186,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6212,7 +6196,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6221,18 +6205,34 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6242,7 +6242,7 @@
         <v>133344422</v>
       </c>
       <c r="B50" t="n">
-        <v>57143</v>
+        <v>57153</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>133566448</v>
       </c>
       <c r="B51" t="n">
-        <v>80481</v>
+        <v>80477</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>133566388</v>
       </c>
       <c r="B52" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>133566389</v>
       </c>
       <c r="B53" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>133566383</v>
       </c>
       <c r="B54" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6817,51 +6817,60 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B55" t="n">
-        <v>79348</v>
+        <v>99178</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R55" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6890,7 +6899,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6900,7 +6909,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6912,21 +6921,6 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6943,60 +6937,51 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B56" t="n">
-        <v>99168</v>
+        <v>79358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R56" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7025,7 +7010,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7035,7 +7020,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7047,6 +7032,21 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -2429,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133344406</v>
+        <v>133344410</v>
       </c>
       <c r="B17" t="n">
-        <v>91957</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,34 +2440,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635433</v>
+        <v>635570</v>
       </c>
       <c r="R17" t="n">
-        <v>6999899</v>
+        <v>6999790</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2499,7 +2507,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2517,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133344410</v>
+        <v>133344406</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,42 +2555,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635570</v>
+        <v>635433</v>
       </c>
       <c r="R18" t="n">
-        <v>6999790</v>
+        <v>6999899</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,7 +2651,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133344397</v>
+        <v>133343519</v>
       </c>
       <c r="B19" t="n">
         <v>91957</v>
@@ -2680,19 +2680,22 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635665</v>
+        <v>635993</v>
       </c>
       <c r="R19" t="n">
-        <v>6999867</v>
+        <v>6999755</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2721,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,18 +2743,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2865,45 +2884,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133344396</v>
+        <v>133344391</v>
       </c>
       <c r="B21" t="n">
-        <v>91920</v>
+        <v>80473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635669</v>
+        <v>635694</v>
       </c>
       <c r="R21" t="n">
-        <v>6999875</v>
+        <v>6999907</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2935,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2967,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2954,8 +2976,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2972,10 +3010,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344391</v>
+        <v>133344397</v>
       </c>
       <c r="B22" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,37 +3021,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635694</v>
+        <v>635665</v>
       </c>
       <c r="R22" t="n">
-        <v>6999907</v>
+        <v>6999867</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3045,7 +3080,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3055,7 +3090,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,24 +3099,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3098,51 +3117,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133343519</v>
+        <v>133344396</v>
       </c>
       <c r="B23" t="n">
-        <v>91957</v>
+        <v>91920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635993</v>
+        <v>635669</v>
       </c>
       <c r="R23" t="n">
-        <v>6999755</v>
+        <v>6999875</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3171,7 +3187,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3197,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,34 +3206,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133343549</v>
+        <v>133344413</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,45 +3569,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635842</v>
+        <v>635804</v>
       </c>
       <c r="R27" t="n">
-        <v>6999727</v>
+        <v>6999795</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3636,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3646,12 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,19 +3653,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344413</v>
+        <v>133344417</v>
       </c>
       <c r="B28" t="n">
         <v>91957</v>
@@ -3713,13 +3700,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635804</v>
+        <v>635820</v>
       </c>
       <c r="R28" t="n">
-        <v>6999795</v>
+        <v>6999730</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3748,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3758,7 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,10 +3772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133344417</v>
+        <v>133343549</v>
       </c>
       <c r="B29" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,37 +3783,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635820</v>
+        <v>635842</v>
       </c>
       <c r="R29" t="n">
-        <v>6999730</v>
+        <v>6999727</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3855,7 +3850,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3860,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,58 +3880,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133344390</v>
+        <v>133344416</v>
       </c>
       <c r="B30" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3939,13 +3930,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635693</v>
+        <v>635824</v>
       </c>
       <c r="R30" t="n">
-        <v>6999909</v>
+        <v>6999739</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3974,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3984,7 +3975,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3996,6 +3987,21 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4012,48 +4018,60 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344398</v>
+        <v>133344390</v>
       </c>
       <c r="B31" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635670</v>
+        <v>635693</v>
       </c>
       <c r="R31" t="n">
-        <v>6999849</v>
+        <v>6999909</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4082,7 +4100,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4092,7 +4110,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4101,6 +4119,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4119,10 +4138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344416</v>
+        <v>133344398</v>
       </c>
       <c r="B32" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4130,37 +4149,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635824</v>
+        <v>635670</v>
       </c>
       <c r="R32" t="n">
-        <v>6999739</v>
+        <v>6999849</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4192,7 +4208,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4202,7 +4218,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,24 +4227,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4245,10 +4245,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133344402</v>
+        <v>133343517</v>
       </c>
       <c r="B33" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>635439</v>
+        <v>636054</v>
       </c>
       <c r="R33" t="n">
-        <v>6999963</v>
+        <v>6999703</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,38 +4343,38 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133343517</v>
+        <v>133344402</v>
       </c>
       <c r="B34" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4409,13 +4409,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636054</v>
+        <v>635439</v>
       </c>
       <c r="R34" t="n">
-        <v>6999703</v>
+        <v>6999963</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4469,28 +4469,28 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5297,60 +5297,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B42" t="n">
-        <v>99178</v>
+        <v>92228</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R42" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5379,7 +5367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5389,7 +5377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5398,67 +5386,78 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B43" t="n">
-        <v>92228</v>
+        <v>99178</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R43" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5487,7 +5486,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,7 +5496,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5506,18 +5505,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5864,64 +5864,51 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133344377</v>
+        <v>133343551</v>
       </c>
       <c r="B47" t="n">
-        <v>58136</v>
+        <v>91920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635919</v>
+        <v>635870</v>
       </c>
       <c r="R47" t="n">
-        <v>6999871</v>
+        <v>6999720</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5950,7 +5937,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5960,7 +5947,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5969,50 +5956,66 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133343551</v>
+        <v>133343547</v>
       </c>
       <c r="B48" t="n">
-        <v>91920</v>
+        <v>91957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6025,10 +6028,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635870</v>
+        <v>635812</v>
       </c>
       <c r="R48" t="n">
-        <v>6999720</v>
+        <v>6999735</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6060,7 +6063,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6070,7 +6073,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6113,10 +6116,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133343547</v>
+        <v>133344377</v>
       </c>
       <c r="B49" t="n">
-        <v>91957</v>
+        <v>58136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6124,40 +6127,53 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635812</v>
+        <v>635919</v>
       </c>
       <c r="R49" t="n">
-        <v>6999735</v>
+        <v>6999871</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6186,7 +6202,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6196,7 +6212,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6205,34 +6221,18 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6354,45 +6354,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566448</v>
+        <v>133566388</v>
       </c>
       <c r="B51" t="n">
-        <v>80477</v>
+        <v>57972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635576</v>
+        <v>635934</v>
       </c>
       <c r="R51" t="n">
-        <v>7000018</v>
+        <v>6999625</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6424,7 +6432,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6442,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6461,53 +6469,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566388</v>
+        <v>133566448</v>
       </c>
       <c r="B52" t="n">
-        <v>57972</v>
+        <v>80477</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635934</v>
+        <v>635576</v>
       </c>
       <c r="R52" t="n">
-        <v>6999625</v>
+        <v>7000018</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6817,60 +6817,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B55" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R55" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6899,7 +6890,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6909,7 +6900,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6921,6 +6912,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6937,51 +6943,60 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B56" t="n">
-        <v>79358</v>
+        <v>99178</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R56" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7010,7 +7025,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7020,7 +7035,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7032,21 +7047,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133343521</v>
+        <v>133343546</v>
       </c>
       <c r="B9" t="n">
-        <v>92228</v>
+        <v>91957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,34 +1500,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635861</v>
+        <v>635817</v>
       </c>
       <c r="R9" t="n">
-        <v>6999964</v>
+        <v>6999735</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1559,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,8 +1581,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133343546</v>
+        <v>133343521</v>
       </c>
       <c r="B10" t="n">
-        <v>91957</v>
+        <v>92228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,37 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635817</v>
+        <v>635861</v>
       </c>
       <c r="R10" t="n">
-        <v>6999735</v>
+        <v>6999964</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1669,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,24 +1704,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2188,42 +2188,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133343531</v>
+        <v>133343516</v>
       </c>
       <c r="B15" t="n">
-        <v>57162</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2231,10 +2226,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635688</v>
+        <v>636049</v>
       </c>
       <c r="R15" t="n">
-        <v>6999888</v>
+        <v>6999689</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2266,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,8 +2280,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2303,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133343516</v>
+        <v>133344406</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,40 +2325,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636049</v>
+        <v>635433</v>
       </c>
       <c r="R16" t="n">
-        <v>6999689</v>
+        <v>6999899</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,7 +2384,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2386,7 +2394,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,34 +2403,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2544,48 +2536,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133344406</v>
+        <v>133343531</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>57162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635433</v>
+        <v>635688</v>
       </c>
       <c r="R18" t="n">
-        <v>6999899</v>
+        <v>6999888</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,12 +2639,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2777,32 +2777,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133344404</v>
+        <v>133344397</v>
       </c>
       <c r="B20" t="n">
-        <v>93254</v>
+        <v>91957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635423</v>
+        <v>635665</v>
       </c>
       <c r="R20" t="n">
-        <v>6999959</v>
+        <v>6999867</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,48 +2884,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133344391</v>
+        <v>133344404</v>
       </c>
       <c r="B21" t="n">
-        <v>80473</v>
+        <v>93254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635694</v>
+        <v>635423</v>
       </c>
       <c r="R21" t="n">
-        <v>6999907</v>
+        <v>6999959</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2957,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,24 +2973,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3010,32 +2991,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133344397</v>
+        <v>133344396</v>
       </c>
       <c r="B22" t="n">
-        <v>91957</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3045,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635665</v>
+        <v>635669</v>
       </c>
       <c r="R22" t="n">
-        <v>6999867</v>
+        <v>6999875</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3080,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3090,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,45 +3098,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133344396</v>
+        <v>133344391</v>
       </c>
       <c r="B23" t="n">
-        <v>91920</v>
+        <v>80473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635669</v>
+        <v>635694</v>
       </c>
       <c r="R23" t="n">
-        <v>6999875</v>
+        <v>6999907</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3187,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3197,7 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,8 +3190,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133344413</v>
+        <v>133343549</v>
       </c>
       <c r="B27" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,37 +3569,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635804</v>
+        <v>635842</v>
       </c>
       <c r="R27" t="n">
-        <v>6999795</v>
+        <v>6999727</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3636,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3646,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,19 +3666,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133344417</v>
+        <v>133344413</v>
       </c>
       <c r="B28" t="n">
         <v>91957</v>
@@ -3700,13 +3713,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635820</v>
+        <v>635804</v>
       </c>
       <c r="R28" t="n">
-        <v>6999730</v>
+        <v>6999795</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,7 +3748,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3758,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,10 +3785,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133343549</v>
+        <v>133344417</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,45 +3796,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635842</v>
+        <v>635820</v>
       </c>
       <c r="R29" t="n">
-        <v>6999727</v>
+        <v>6999730</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3850,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3860,12 +3865,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,49 +3880,58 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133344416</v>
+        <v>133344390</v>
       </c>
       <c r="B30" t="n">
-        <v>79358</v>
+        <v>99178</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3930,13 +3939,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635824</v>
+        <v>635693</v>
       </c>
       <c r="R30" t="n">
-        <v>6999739</v>
+        <v>6999909</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3965,7 +3974,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3984,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3987,21 +3996,6 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4018,60 +4012,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133344390</v>
+        <v>133344398</v>
       </c>
       <c r="B31" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635693</v>
+        <v>635670</v>
       </c>
       <c r="R31" t="n">
-        <v>6999909</v>
+        <v>6999849</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,7 +4082,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4110,7 +4092,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4119,7 +4101,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4138,10 +4119,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133344398</v>
+        <v>133344416</v>
       </c>
       <c r="B32" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4149,34 +4130,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>635670</v>
+        <v>635824</v>
       </c>
       <c r="R32" t="n">
-        <v>6999849</v>
+        <v>6999739</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4208,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4218,7 +4202,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4227,8 +4211,24 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4834,7 +4834,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133343548</v>
+        <v>133344407</v>
       </c>
       <c r="B38" t="n">
         <v>79358</v>
@@ -4863,19 +4863,22 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635839</v>
+        <v>635393</v>
       </c>
       <c r="R38" t="n">
-        <v>6999729</v>
+        <v>6999887</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4904,7 +4907,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4914,7 +4917,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4923,28 +4926,44 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133343536</v>
+        <v>133343548</v>
       </c>
       <c r="B39" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4952,42 +4971,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635415</v>
+        <v>635839</v>
       </c>
       <c r="R39" t="n">
-        <v>6999961</v>
+        <v>6999729</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5019,7 +5030,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5029,7 +5040,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5056,10 +5067,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133344407</v>
+        <v>133343536</v>
       </c>
       <c r="B40" t="n">
-        <v>79358</v>
+        <v>57972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5067,26 +5078,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5094,13 +5110,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635393</v>
+        <v>635415</v>
       </c>
       <c r="R40" t="n">
-        <v>6999887</v>
+        <v>6999961</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5129,7 +5145,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5139,7 +5155,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5148,34 +5164,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6354,53 +6354,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566388</v>
+        <v>133566448</v>
       </c>
       <c r="B51" t="n">
-        <v>57972</v>
+        <v>80477</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635934</v>
+        <v>635576</v>
       </c>
       <c r="R51" t="n">
-        <v>6999625</v>
+        <v>7000018</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6432,7 +6424,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6442,7 +6434,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6469,45 +6461,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566448</v>
+        <v>133566388</v>
       </c>
       <c r="B52" t="n">
-        <v>80477</v>
+        <v>57972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635576</v>
+        <v>635934</v>
       </c>
       <c r="R52" t="n">
-        <v>7000018</v>
+        <v>6999625</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6817,51 +6817,60 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133573131</v>
+        <v>133573160</v>
       </c>
       <c r="B55" t="n">
-        <v>79358</v>
+        <v>99178</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjuvdoberget, Ång</t>
+          <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635838</v>
+        <v>635279</v>
       </c>
       <c r="R55" t="n">
-        <v>6999713</v>
+        <v>6999958</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6890,7 +6899,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6900,7 +6909,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6912,21 +6921,6 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6943,60 +6937,51 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133573160</v>
+        <v>133573131</v>
       </c>
       <c r="B56" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tjuvtoberget, Ång</t>
+          <t>Tjuvdoberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635279</v>
+        <v>635838</v>
       </c>
       <c r="R56" t="n">
-        <v>6999958</v>
+        <v>6999713</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7025,7 +7010,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7035,7 +7020,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7047,6 +7032,21 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133343546</v>
+        <v>133343521</v>
       </c>
       <c r="B9" t="n">
-        <v>91957</v>
+        <v>92228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,37 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635817</v>
+        <v>635861</v>
       </c>
       <c r="R9" t="n">
-        <v>6999735</v>
+        <v>6999964</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1562,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,24 +1578,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1615,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133343521</v>
+        <v>133343546</v>
       </c>
       <c r="B10" t="n">
-        <v>92228</v>
+        <v>91957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,34 +1607,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635861</v>
+        <v>635817</v>
       </c>
       <c r="R10" t="n">
-        <v>6999964</v>
+        <v>6999735</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,8 +1688,24 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -4245,10 +4245,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133343517</v>
+        <v>133344402</v>
       </c>
       <c r="B33" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636054</v>
+        <v>635439</v>
       </c>
       <c r="R33" t="n">
-        <v>6999703</v>
+        <v>6999963</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,38 +4343,38 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133344402</v>
+        <v>133343517</v>
       </c>
       <c r="B34" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4409,13 +4409,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>635439</v>
+        <v>636054</v>
       </c>
       <c r="R34" t="n">
-        <v>6999963</v>
+        <v>6999703</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4469,28 +4469,28 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4834,7 +4834,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133344407</v>
+        <v>133343548</v>
       </c>
       <c r="B38" t="n">
         <v>79358</v>
@@ -4863,22 +4863,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>635393</v>
+        <v>635839</v>
       </c>
       <c r="R38" t="n">
-        <v>6999887</v>
+        <v>6999729</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4907,7 +4904,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4917,7 +4914,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4926,44 +4923,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133343548</v>
+        <v>133343536</v>
       </c>
       <c r="B39" t="n">
-        <v>79358</v>
+        <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4971,34 +4952,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>635839</v>
+        <v>635415</v>
       </c>
       <c r="R39" t="n">
-        <v>6999729</v>
+        <v>6999961</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5030,7 +5019,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5040,7 +5029,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5067,10 +5056,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133343536</v>
+        <v>133344407</v>
       </c>
       <c r="B40" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5078,31 +5067,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5110,13 +5094,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>635415</v>
+        <v>635393</v>
       </c>
       <c r="R40" t="n">
-        <v>6999961</v>
+        <v>6999887</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5145,7 +5129,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5139,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5164,18 +5148,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5297,48 +5297,60 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133343518</v>
+        <v>133344423</v>
       </c>
       <c r="B42" t="n">
-        <v>92228</v>
+        <v>99178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636016</v>
+        <v>635865</v>
       </c>
       <c r="R42" t="n">
-        <v>6999762</v>
+        <v>6999709</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5367,7 +5379,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5386,78 +5398,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133344423</v>
+        <v>133343518</v>
       </c>
       <c r="B43" t="n">
-        <v>99178</v>
+        <v>92228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjuvtoberget-Karberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>635865</v>
+        <v>636016</v>
       </c>
       <c r="R43" t="n">
-        <v>6999709</v>
+        <v>6999762</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5486,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5496,7 +5497,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,19 +5506,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 4526-2026 artfynd.xlsx
+++ b/artfynd/A 4526-2026 artfynd.xlsx
@@ -6354,45 +6354,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133566448</v>
+        <v>133566389</v>
       </c>
       <c r="B51" t="n">
-        <v>80477</v>
+        <v>57972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635576</v>
+        <v>635931</v>
       </c>
       <c r="R51" t="n">
-        <v>7000018</v>
+        <v>6999628</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6424,7 +6432,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6434,7 +6442,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6461,53 +6469,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133566388</v>
+        <v>133566448</v>
       </c>
       <c r="B52" t="n">
-        <v>57972</v>
+        <v>80478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635934</v>
+        <v>635576</v>
       </c>
       <c r="R52" t="n">
-        <v>6999625</v>
+        <v>7000018</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6576,7 +6576,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133566389</v>
+        <v>133566388</v>
       </c>
       <c r="B53" t="n">
         <v>57972</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635931</v>
+        <v>635934</v>
       </c>
       <c r="R53" t="n">
-        <v>6999628</v>
+        <v>6999625</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6694,7 +6694,7 @@
         <v>133566383</v>
       </c>
       <c r="B54" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>133573160</v>
       </c>
       <c r="B55" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>133573131</v>
       </c>
       <c r="B56" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
